--- a/data/input/kalpa-songs.xlsx
+++ b/data/input/kalpa-songs.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aqua_\git\kalpa-selection\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A500FE52-367A-475D-BF65-16F5D450433E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A705EE-4D16-4D60-B193-B098CCB6C50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-17295" yWindow="2940" windowWidth="17235" windowHeight="11835" xr2:uid="{B18DF0BD-955E-4CF1-A738-32182884837D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$144</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="282">
   <si>
     <t>id</t>
   </si>
@@ -66,84 +69,993 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>∀</t>
-    <phoneticPr fontId="1"/>
+    <t>Lemuria</t>
+  </si>
+  <si>
+    <t>xi</t>
+  </si>
+  <si>
+    <t>EXILE</t>
+  </si>
+  <si>
+    <t>キミとボクへの葬送歌</t>
+  </si>
+  <si>
+    <t>Rokina</t>
+  </si>
+  <si>
+    <t>Legacy</t>
+  </si>
+  <si>
+    <t>Jehezukiel</t>
+  </si>
+  <si>
+    <t>HAELEQ∩INZ -the clown of 24stairs-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>orangentle / Yu_Asahina</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>First Forte</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BRAVE : ROAD</t>
+  </si>
+  <si>
+    <t>uma vs. モリモリあつし</t>
+  </si>
+  <si>
+    <t>LINK x LIN#S</t>
+  </si>
+  <si>
+    <t>Halv</t>
+  </si>
+  <si>
+    <t>Vicious Mockery</t>
+  </si>
+  <si>
+    <t>Kry.exe</t>
+  </si>
+  <si>
+    <t>Lost Future</t>
+  </si>
+  <si>
+    <t>Aspid Cat</t>
+  </si>
+  <si>
+    <t>Dot-Line (short ver.)</t>
+  </si>
+  <si>
+    <t>A-39 &amp; 沙包P &amp; ななひら</t>
+  </si>
+  <si>
+    <t>Rizline Collaboration Pack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Lanota Collaboration Pack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Astaroth</t>
+  </si>
+  <si>
+    <t>Team Grimoire</t>
+  </si>
+  <si>
+    <t>Wolves Standing Towards Enemies</t>
+  </si>
+  <si>
+    <t>Camellia(EDP)</t>
+  </si>
+  <si>
+    <t>You are the Miserable</t>
+  </si>
+  <si>
+    <t>t+pazolite</t>
+  </si>
+  <si>
+    <t>ΤεμπεΣΤ</t>
+  </si>
+  <si>
+    <t>Zekk</t>
+  </si>
+  <si>
+    <t>monolith</t>
+  </si>
+  <si>
+    <t>Takenoko boy feat. metyao</t>
+  </si>
+  <si>
+    <t>Deeeer Simulator Collaboration Pack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ragnarok (Roy Mikelate Remix)</t>
+  </si>
+  <si>
+    <t>Earliri</t>
+  </si>
+  <si>
+    <t>Deathfight 3rd</t>
+  </si>
+  <si>
+    <t>GANO</t>
+  </si>
+  <si>
+    <t>Battle for the future</t>
+  </si>
+  <si>
+    <t>ieri</t>
+  </si>
+  <si>
+    <t>Neon Walk</t>
+  </si>
+  <si>
+    <t>Kuripper</t>
+  </si>
+  <si>
+    <t>WToF (Keyboard-Breaking Mix)</t>
+  </si>
+  <si>
+    <t>Scarlette</t>
+  </si>
+  <si>
+    <t>SixtarGate Collaboration Pack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Into a Frenzy</t>
+  </si>
+  <si>
+    <t>Masahiro "Godspeed" Aoki</t>
+  </si>
+  <si>
+    <t>STARGATE EXTREME</t>
+  </si>
+  <si>
+    <t>KARUT</t>
+  </si>
+  <si>
+    <t>Moon And Back</t>
+  </si>
+  <si>
+    <t>RiraN</t>
+  </si>
+  <si>
+    <t>Bossfire</t>
+  </si>
+  <si>
+    <t>Roy Mikelate feat. ATAS</t>
+  </si>
+  <si>
+    <t>Andromeda 02 ~Avantgarde~</t>
+  </si>
+  <si>
+    <t>Sound Souler</t>
+  </si>
+  <si>
+    <t>Antinomic Queen</t>
+  </si>
+  <si>
+    <t>polysha</t>
+  </si>
+  <si>
+    <t>Eranthis</t>
+  </si>
+  <si>
+    <t>LucaProject</t>
+  </si>
+  <si>
+    <t>StellaR-MemoriA</t>
+  </si>
+  <si>
+    <t>Raphiiel</t>
+  </si>
+  <si>
+    <t>Phigros Collaboration Pack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Distorted Fate</t>
+  </si>
+  <si>
+    <t>Sakuzyo</t>
+  </si>
+  <si>
+    <t>Rrhar'il</t>
+  </si>
+  <si>
+    <t>Igallta</t>
+  </si>
+  <si>
+    <t>Se-U-Ra</t>
+  </si>
+  <si>
+    <t>DESTRUCTION 3,2,1</t>
+  </si>
+  <si>
+    <t>Normal1zer vs. Broken Nerdz</t>
+  </si>
+  <si>
+    <t>NO ONE YES MAN</t>
+  </si>
+  <si>
+    <t>MYUKKE.</t>
+  </si>
+  <si>
+    <t>Concvssion</t>
+  </si>
+  <si>
+    <t>Snow Desert</t>
+  </si>
+  <si>
+    <t>WyvernP</t>
+  </si>
+  <si>
+    <t>A-39</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雪降り、メリクリ(Snowfall and Merry Chrishmas)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mass Recall Omega</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Aci-L (Since04’orangentle Remix)</t>
+  </si>
+  <si>
+    <t>Brain Power(Cranky Remix)</t>
+  </si>
+  <si>
+    <t>DataErr0r (Crimson Cyberpunk Mix)</t>
+  </si>
+  <si>
+    <t>GOODBOUNCE (Drunk Remix)</t>
+  </si>
+  <si>
+    <t>GOODRAGE (seatrus 海ックス)</t>
+  </si>
+  <si>
+    <t>Halcyon (MRM REMIX)</t>
+  </si>
+  <si>
+    <t>xi Remixed by モリモリあつし</t>
+  </si>
+  <si>
+    <t>SHIKI Remixed by Ice</t>
+  </si>
+  <si>
+    <t>Ophelia -Phantasm-</t>
+  </si>
+  <si>
+    <t>PUPA (Endorfin. Remix)</t>
+  </si>
+  <si>
+    <t>モリモリあつし Remixed by Endorfin.</t>
+  </si>
+  <si>
+    <t>PUPA (Sakuzyo Latin Remix)</t>
+  </si>
+  <si>
+    <t>モリモリあつし Remixed by Sakuzyo</t>
+  </si>
+  <si>
+    <t>The Formula (HISPEED REMIX)</t>
+  </si>
+  <si>
+    <t>The Last Page (ESAI Remix)</t>
+  </si>
+  <si>
+    <t>PUPA (GRG REMIX)</t>
+  </si>
+  <si>
+    <t>モリモリあつし Remixed by ガリガリさむし</t>
+  </si>
+  <si>
+    <t>orangentle</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Scarlette</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>seatrus</t>
+  </si>
+  <si>
+    <t>seatrus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>Äventyr (Seir</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ḗ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>n Mix)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - JP ver.</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Sera Amagi </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>Äventyr (Seir</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ḗ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>n Mix) prod. Yuukineko</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MYULee feat. Sera Amagi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Lapis (Ice Respect Remix)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>もぺもぺ(Roy Mikelate Remix)(Mopemope)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Roy Mikelate</t>
+  </si>
+  <si>
+    <t>Roy Mikelate</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EBIMAYO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Lime</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Junk</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ESAI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cranky</t>
+  </si>
+  <si>
+    <t>Cranky</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rotaeno Collaboration Pack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Maholova</t>
+  </si>
+  <si>
+    <t>aran</t>
+  </si>
+  <si>
+    <t>GALACTIC WARZONE</t>
+  </si>
+  <si>
+    <t>Akira Complex</t>
+  </si>
+  <si>
+    <t>Spinel</t>
+  </si>
+  <si>
+    <t>ぺのれり</t>
+  </si>
+  <si>
+    <t>Secret Illumination</t>
+  </si>
+  <si>
+    <t>Yooh</t>
+  </si>
+  <si>
+    <t>Waltz for Lorelei</t>
+  </si>
+  <si>
+    <t>Sobrem &amp; 庭師</t>
+  </si>
+  <si>
+    <t>Inverted World</t>
+  </si>
+  <si>
+    <t>ARForest</t>
+  </si>
+  <si>
+    <t>HyuN feat. kradness</t>
+  </si>
+  <si>
+    <t>HyuN feat. ウォルピスカーター</t>
+  </si>
+  <si>
+    <t>Calorific Refract</t>
+  </si>
+  <si>
+    <t>Tatsh</t>
+  </si>
+  <si>
+    <t>Secret Illumination (seatrus's “The AURA” Remix)</t>
+  </si>
+  <si>
+    <t>The Promised Land</t>
+  </si>
+  <si>
+    <t>Iris feat. LynH</t>
+  </si>
+  <si>
+    <t>無彩色のディストピア(Achromatci Dystopia)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>極彩色のユートピア(Gokusaisoku no Utopia)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Origin Vol.1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pang Pang Fanfare</t>
+  </si>
+  <si>
+    <t>Kizuna</t>
+  </si>
+  <si>
+    <t>RiraN feat. 音琴兎愛</t>
+  </si>
+  <si>
+    <t>Take Me Beyond</t>
+  </si>
+  <si>
+    <t>Light into Heart</t>
+  </si>
+  <si>
+    <t>Nauts</t>
+  </si>
+  <si>
+    <t>The Evacuation</t>
+  </si>
+  <si>
+    <t>Planetboom</t>
+  </si>
+  <si>
+    <t>Oblivion Lotus</t>
+  </si>
+  <si>
+    <t>wa.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Burnfire feat. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>문모모</t>
+    </r>
+  </si>
+  <si>
+    <t>Roy Mikelate &amp; FidgetSpinny</t>
+  </si>
+  <si>
+    <t>Deep Blue Wave</t>
+  </si>
+  <si>
+    <t>Yesod</t>
+  </si>
+  <si>
+    <t>Doin</t>
+  </si>
+  <si>
+    <t>Réfraction d'eau, Op. 3</t>
+  </si>
+  <si>
+    <t>Raimukun</t>
+  </si>
+  <si>
+    <t>Mitsukiyo &amp; seibin</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무지개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rainbow Reflex)</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Paradigm: Reboot Collaboration Pack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mystical Observer</t>
+  </si>
+  <si>
+    <t>DJ Myosuke</t>
+  </si>
+  <si>
+    <t>Awakening of Civilization</t>
+  </si>
+  <si>
+    <t>黒魔</t>
+  </si>
+  <si>
+    <t>ma[χ]zo</t>
+  </si>
+  <si>
+    <t>Viyella's Melancholy</t>
+  </si>
+  <si>
+    <t>Laur</t>
+  </si>
+  <si>
+    <t>Restricted Access</t>
+  </si>
+  <si>
+    <t>Knighthood</t>
+  </si>
+  <si>
+    <t>Notanote Collaboration Pack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>cybernetic blazar</t>
   </si>
   <si>
     <t>ああああ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>¢orrupted ar¢hetype</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Lauridsen &amp; VOiD</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.566×10^80m3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Apo11o program vs. Ice ft.朧-oboro-</t>
-    <rPh sb="26" eb="27">
-      <t>オボロ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>420mb (Game Edit)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ariiol</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Aci-L (Remaster)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Aci-L (since04' orangentle Remix)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>orangentle</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Alice in Misanthrope -厭世アリス-</t>
-    <rPh sb="22" eb="23">
-      <t>イヤ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>LeaF</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Altale</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>削除(Sakuzyo)</t>
-    <rPh sb="0" eb="2">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Daughter of Daedalus</t>
+  </si>
+  <si>
+    <t>tn-shi</t>
+  </si>
+  <si>
+    <t>Innocent white</t>
+  </si>
+  <si>
+    <t>Kagetora.</t>
+  </si>
+  <si>
+    <t>Berry Melody Collaboration Pack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bright red hertz</t>
+  </si>
+  <si>
+    <t>Kagetora. feat. Shabel Tonya</t>
+  </si>
+  <si>
+    <t>ЯеИatus</t>
+  </si>
+  <si>
+    <t>天束 feat.ぽめ</t>
+  </si>
+  <si>
+    <t>HATEN CODE 583</t>
+  </si>
+  <si>
+    <t>Grayscale Tragedy</t>
+  </si>
+  <si>
+    <t>Polysha</t>
+  </si>
+  <si>
+    <t>Black and White Monster</t>
+  </si>
+  <si>
+    <t>Tezuka</t>
+  </si>
+  <si>
+    <t>Camellia Pack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Camellia</t>
+  </si>
+  <si>
+    <t>ベースラインやってる？笑</t>
+  </si>
+  <si>
+    <t>GHOST (Game Edit)</t>
+  </si>
+  <si>
+    <t>Dance with Silence</t>
+  </si>
+  <si>
+    <t>+ERABY+E CONNEC+10N</t>
+  </si>
+  <si>
+    <t>Body F10ating in the Zero Gravity Space</t>
+  </si>
+  <si>
+    <t>Flamewall (Original Mix)</t>
+  </si>
+  <si>
+    <t>GHOST (Original Mix)</t>
+  </si>
+  <si>
+    <t>M1LLI0N PP (Original Mix)</t>
+  </si>
+  <si>
+    <t>ヒアソビ(Play-With-Fire/Hiasobi)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Flamewall (Game Edit)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>M1LLI0N PP (Game Edit)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Compute It With Some Devilish Alcoholic Steampunk Engines</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>To the Moon Collaboration Pack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>For River - Piano (Johnny's Version)</t>
+  </si>
+  <si>
+    <t>Kan Gao</t>
+  </si>
+  <si>
+    <t>To the Moon Main Theme</t>
+  </si>
+  <si>
+    <t>Faye's Theme (Paper Memories Vers.)</t>
+  </si>
+  <si>
+    <t>Lullaby from a Star</t>
+  </si>
+  <si>
+    <t>Kan Gao, feat. Pealeaf</t>
+  </si>
+  <si>
+    <t>Our Waltz To the Moon</t>
+  </si>
+  <si>
+    <t>Second Forte Pack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Overwrite (feat. 月乃)</t>
+  </si>
+  <si>
+    <t>INFX</t>
+  </si>
+  <si>
+    <t>Sadalsuud</t>
+  </si>
+  <si>
+    <t>Evin a'k</t>
+  </si>
+  <si>
+    <t>MilK</t>
+  </si>
+  <si>
+    <t>モリモリあつし</t>
+  </si>
+  <si>
+    <t>Your Mind</t>
+  </si>
+  <si>
+    <t>Pica Pica</t>
+  </si>
+  <si>
+    <t>horoscope a.k.a. LUZE</t>
+  </si>
+  <si>
+    <t>OMG</t>
+  </si>
+  <si>
+    <t>Black Region</t>
+  </si>
+  <si>
+    <t>G e n g a o z o</t>
+  </si>
+  <si>
+    <t>Sera Amagi</t>
+  </si>
+  <si>
+    <t>kintsugi</t>
+  </si>
+  <si>
+    <t>Iris</t>
+  </si>
+  <si>
+    <t>VERUM - proximus</t>
+  </si>
+  <si>
+    <t>Origin Vol. 2 Pack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Wipe Until It Hurts</t>
+  </si>
+  <si>
+    <t>TORIENA</t>
+  </si>
+  <si>
+    <t>CLIMAX9999</t>
+  </si>
+  <si>
+    <t>Blacklolita</t>
+  </si>
+  <si>
+    <t>VIKTØRIA</t>
+  </si>
+  <si>
+    <t>Tatsunoshin</t>
+  </si>
+  <si>
+    <t>Ventora Nova</t>
+  </si>
+  <si>
+    <t>Better than Yesterday feat. NC.A</t>
+  </si>
+  <si>
+    <t>Colourful Diving!</t>
+  </si>
+  <si>
+    <t>天束</t>
+  </si>
+  <si>
+    <t>立秋 feat.ちょこ</t>
+  </si>
+  <si>
+    <t>DURAND4L</t>
+  </si>
+  <si>
+    <t>Vale</t>
+  </si>
+  <si>
+    <t>削除 (Sakuzyo)</t>
+  </si>
+  <si>
+    <t>Capchii</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hyper Math feat. utumiyqcom</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>か(KA)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Third Forte Pack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Reload Future (feat.タイココちゃんねる)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morgenglut 2012 </t>
+  </si>
+  <si>
+    <t>sun3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flugel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ctrl + Alt + Del </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retaliation </t>
+  </si>
+  <si>
+    <t>Juggernaut.</t>
+  </si>
+  <si>
+    <t>skip&amp;step</t>
+  </si>
+  <si>
+    <t>Mono.</t>
+  </si>
+  <si>
+    <t>BASTET</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Jehezukiel</t>
+  </si>
+  <si>
+    <t>Boxel Adventure</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7mai</t>
+  </si>
+  <si>
+    <t>Satellite Adventure</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> pan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-Arkhēi- </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> INFX &amp; MIIM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fourth Forte Pack</t>
+  </si>
+  <si>
+    <t>タイムカプセル</t>
+  </si>
+  <si>
+    <t>Project "Blue Bird"</t>
+  </si>
+  <si>
+    <t>夏色レモンタルト Feat.薛南</t>
+  </si>
+  <si>
+    <t>XinG</t>
   </si>
   <si>
     <t>Amphetamine</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>MonstDeath vs Neutral Moon</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>sut</t>
+  </si>
+  <si>
+    <t>HADALI</t>
+  </si>
+  <si>
+    <t>Kaede Hiyama (feat. Real)</t>
+  </si>
+  <si>
+    <t>Night Shift</t>
+  </si>
+  <si>
+    <t>PTB10</t>
+  </si>
+  <si>
+    <t>FORTALiCE</t>
+  </si>
+  <si>
+    <t>ZxNX</t>
+  </si>
+  <si>
+    <t>iRELLiA</t>
+  </si>
+  <si>
+    <t>HyuN</t>
+  </si>
+  <si>
+    <t>Skyline</t>
+  </si>
+  <si>
+    <t>Koto Spirit</t>
+  </si>
+  <si>
+    <t>Jehezukiel &amp; KURORAK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Freaky Undulations ~Noble Knights of The Tune~</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -151,7 +1063,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -166,6 +1078,50 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -190,8 +1146,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -528,7 +1487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F48EBC91-EB0A-4513-A427-E3024C547FB9}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" bestFit="1" customWidth="1"/>
@@ -569,22 +1528,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>193</v>
       </c>
       <c r="C2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E2">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
       <c r="F2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
@@ -592,19 +1551,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="E3">
         <v>8</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>18</v>
@@ -615,22 +1574,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>268</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>269</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>263</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>13</v>
       </c>
       <c r="G4">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -638,22 +1597,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="E5">
         <v>6</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
@@ -661,22 +1620,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6">
-        <v>-45</v>
+        <v>62</v>
+      </c>
+      <c r="C6" t="s">
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="E6">
         <v>6</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
@@ -684,22 +1643,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>261</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>223</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>245</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
@@ -707,19 +1666,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
       <c r="F8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>17</v>
@@ -730,22 +1689,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
@@ -753,25 +1712,3112 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10">
+        <v>12</v>
+      </c>
+      <c r="G10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E11">
+        <v>6</v>
+      </c>
+      <c r="F11">
+        <v>13</v>
+      </c>
+      <c r="G11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C12" t="s">
+        <v>256</v>
+      </c>
+      <c r="D12" t="s">
+        <v>245</v>
+      </c>
+      <c r="E12">
+        <v>6</v>
+      </c>
+      <c r="F12">
+        <v>12</v>
+      </c>
+      <c r="G12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13">
+        <v>7</v>
+      </c>
+      <c r="F13">
+        <v>9</v>
+      </c>
+      <c r="G13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>235</v>
+      </c>
+      <c r="C14" t="s">
+        <v>212</v>
+      </c>
+      <c r="D14" t="s">
+        <v>227</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14">
+        <v>11</v>
+      </c>
+      <c r="G14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>186</v>
+      </c>
+      <c r="C15" t="s">
+        <v>187</v>
+      </c>
+      <c r="D15" t="s">
+        <v>178</v>
+      </c>
+      <c r="E15">
+        <v>7</v>
+      </c>
+      <c r="F15">
+        <v>13</v>
+      </c>
+      <c r="G15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>221</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" t="s">
+        <v>210</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+      <c r="F16">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>194</v>
+      </c>
+      <c r="C17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D17" t="s">
+        <v>188</v>
+      </c>
+      <c r="E17">
+        <v>6</v>
+      </c>
+      <c r="F17">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18">
+        <v>9</v>
+      </c>
+      <c r="F18">
+        <v>15</v>
+      </c>
+      <c r="G18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>257</v>
+      </c>
+      <c r="C19" t="s">
+        <v>258</v>
+      </c>
+      <c r="D19" t="s">
+        <v>245</v>
+      </c>
+      <c r="E19">
+        <v>8</v>
+      </c>
+      <c r="F19">
+        <v>14</v>
+      </c>
+      <c r="G19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20">
+        <v>12</v>
+      </c>
+      <c r="G20">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21">
+        <v>7</v>
+      </c>
+      <c r="F21">
+        <v>14</v>
+      </c>
+      <c r="G21">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" t="s">
+        <v>180</v>
+      </c>
+      <c r="D22" t="s">
+        <v>178</v>
+      </c>
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="F22">
+        <v>10</v>
+      </c>
+      <c r="G22">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>152</v>
+      </c>
+      <c r="C23" t="s">
+        <v>153</v>
+      </c>
+      <c r="D23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E23">
+        <v>6</v>
+      </c>
+      <c r="F23">
+        <v>13</v>
+      </c>
+      <c r="G23">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B24" t="s">
+        <v>134</v>
+      </c>
+      <c r="C24" t="s">
+        <v>135</v>
+      </c>
+      <c r="D24" t="s">
+        <v>119</v>
+      </c>
+      <c r="E24">
+        <v>7</v>
+      </c>
+      <c r="F24">
+        <v>15</v>
+      </c>
+      <c r="G24">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="D10" t="s">
+      <c r="B25" t="s">
+        <v>230</v>
+      </c>
+      <c r="C25" t="s">
+        <v>231</v>
+      </c>
+      <c r="D25" t="s">
+        <v>227</v>
+      </c>
+      <c r="E25">
+        <v>6</v>
+      </c>
+      <c r="F25">
+        <v>13</v>
+      </c>
+      <c r="G25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="E10">
+      <c r="B26" t="s">
+        <v>236</v>
+      </c>
+      <c r="C26" t="s">
+        <v>237</v>
+      </c>
+      <c r="D26" t="s">
+        <v>227</v>
+      </c>
+      <c r="E26">
+        <v>5</v>
+      </c>
+      <c r="F26">
+        <v>10</v>
+      </c>
+      <c r="G26">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C27" t="s">
+        <v>189</v>
+      </c>
+      <c r="D27" t="s">
+        <v>188</v>
+      </c>
+      <c r="E27">
+        <v>7</v>
+      </c>
+      <c r="F27">
+        <v>13</v>
+      </c>
+      <c r="G27">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28">
+        <v>6</v>
+      </c>
+      <c r="F28">
+        <v>14</v>
+      </c>
+      <c r="G28">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>250</v>
+      </c>
+      <c r="C29" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" t="s">
+        <v>245</v>
+      </c>
+      <c r="E29">
+        <v>6</v>
+      </c>
+      <c r="F29">
+        <v>10</v>
+      </c>
+      <c r="G29">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" t="s">
+        <v>173</v>
+      </c>
+      <c r="D30" t="s">
+        <v>171</v>
+      </c>
+      <c r="E30">
+        <v>6</v>
+      </c>
+      <c r="F30">
+        <v>12</v>
+      </c>
+      <c r="G30">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>192</v>
+      </c>
+      <c r="C31" t="s">
+        <v>189</v>
+      </c>
+      <c r="D31" t="s">
+        <v>188</v>
+      </c>
+      <c r="E31">
+        <v>5</v>
+      </c>
+      <c r="F31">
+        <v>11</v>
+      </c>
+      <c r="G31">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" t="s">
+        <v>102</v>
+      </c>
+      <c r="D32" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32">
+        <v>6</v>
+      </c>
+      <c r="F32">
+        <v>12</v>
+      </c>
+      <c r="G32">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>174</v>
+      </c>
+      <c r="C33" t="s">
+        <v>175</v>
+      </c>
+      <c r="D33" t="s">
+        <v>171</v>
+      </c>
+      <c r="E33">
+        <v>7</v>
+      </c>
+      <c r="F33">
+        <v>12</v>
+      </c>
+      <c r="G33">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34">
+        <v>6</v>
+      </c>
+      <c r="F34">
+        <v>13</v>
+      </c>
+      <c r="G34">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>154</v>
+      </c>
+      <c r="C35" t="s">
+        <v>155</v>
+      </c>
+      <c r="D35" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35">
+        <v>7</v>
+      </c>
+      <c r="F35">
+        <v>13</v>
+      </c>
+      <c r="G35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" t="s">
+        <v>68</v>
+      </c>
+      <c r="E36">
+        <v>9</v>
+      </c>
+      <c r="F36">
+        <v>15</v>
+      </c>
+      <c r="G36">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37">
+        <v>7</v>
+      </c>
+      <c r="F37">
+        <v>14</v>
+      </c>
+      <c r="G37">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" t="s">
+        <v>28</v>
+      </c>
+      <c r="E38">
+        <v>3</v>
+      </c>
+      <c r="F38">
+        <v>11</v>
+      </c>
+      <c r="G38">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>239</v>
+      </c>
+      <c r="C39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" t="s">
+        <v>227</v>
+      </c>
+      <c r="E39">
+        <v>10</v>
+      </c>
+      <c r="F39">
+        <v>16</v>
+      </c>
+      <c r="G39">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40">
+        <v>4</v>
+      </c>
+      <c r="F40">
+        <v>11</v>
+      </c>
+      <c r="G40">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41">
+        <v>-45</v>
+      </c>
+      <c r="D41" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41">
+        <v>7</v>
+      </c>
+      <c r="F41">
+        <v>14</v>
+      </c>
+      <c r="G41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>206</v>
+      </c>
+      <c r="C42" t="s">
+        <v>204</v>
+      </c>
+      <c r="D42" t="s">
+        <v>202</v>
+      </c>
+      <c r="E42">
+        <v>4</v>
+      </c>
+      <c r="F42">
         <v>8</v>
       </c>
-      <c r="F10">
+      <c r="G42">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>199</v>
+      </c>
+      <c r="C43" t="s">
+        <v>189</v>
+      </c>
+      <c r="D43" t="s">
+        <v>188</v>
+      </c>
+      <c r="E43">
+        <v>7</v>
+      </c>
+      <c r="F43">
+        <v>14</v>
+      </c>
+      <c r="G43">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>195</v>
+      </c>
+      <c r="C44" t="s">
+        <v>189</v>
+      </c>
+      <c r="D44" t="s">
+        <v>188</v>
+      </c>
+      <c r="E44">
+        <v>7</v>
+      </c>
+      <c r="F44">
+        <v>14</v>
+      </c>
+      <c r="G44">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>249</v>
+      </c>
+      <c r="C45" t="s">
+        <v>117</v>
+      </c>
+      <c r="D45" t="s">
+        <v>245</v>
+      </c>
+      <c r="E45">
+        <v>5</v>
+      </c>
+      <c r="F45">
+        <v>12</v>
+      </c>
+      <c r="G45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>203</v>
+      </c>
+      <c r="C46" t="s">
+        <v>204</v>
+      </c>
+      <c r="D46" t="s">
+        <v>202</v>
+      </c>
+      <c r="E46">
+        <v>3</v>
+      </c>
+      <c r="F46">
+        <v>5</v>
+      </c>
+      <c r="G46">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>274</v>
+      </c>
+      <c r="C47" t="s">
+        <v>275</v>
+      </c>
+      <c r="D47" t="s">
+        <v>263</v>
+      </c>
+      <c r="E47">
+        <v>8</v>
+      </c>
+      <c r="F47">
+        <v>14</v>
+      </c>
+      <c r="G47">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>281</v>
+      </c>
+      <c r="C48" t="s">
+        <v>280</v>
+      </c>
+      <c r="D48" t="s">
+        <v>263</v>
+      </c>
+      <c r="E48">
+        <v>7</v>
+      </c>
+      <c r="F48">
         <v>13</v>
       </c>
-      <c r="G10">
-        <v>17</v>
+      <c r="G48">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>222</v>
+      </c>
+      <c r="C49">
+        <v>-45</v>
+      </c>
+      <c r="D49" t="s">
+        <v>210</v>
+      </c>
+      <c r="E49">
+        <v>7</v>
+      </c>
+      <c r="F49">
+        <v>14</v>
+      </c>
+      <c r="G49">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>122</v>
+      </c>
+      <c r="C50" t="s">
+        <v>123</v>
+      </c>
+      <c r="D50" t="s">
+        <v>119</v>
+      </c>
+      <c r="E50">
+        <v>7</v>
+      </c>
+      <c r="F50">
+        <v>15</v>
+      </c>
+      <c r="G50">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>191</v>
+      </c>
+      <c r="C51" t="s">
+        <v>189</v>
+      </c>
+      <c r="D51" t="s">
+        <v>188</v>
+      </c>
+      <c r="E51">
+        <v>6</v>
+      </c>
+      <c r="F51">
+        <v>13</v>
+      </c>
+      <c r="G51">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>196</v>
+      </c>
+      <c r="C52" t="s">
+        <v>189</v>
+      </c>
+      <c r="D52" t="s">
+        <v>188</v>
+      </c>
+      <c r="E52">
+        <v>6</v>
+      </c>
+      <c r="F52">
+        <v>13</v>
+      </c>
+      <c r="G52">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>87</v>
+      </c>
+      <c r="C53" t="s">
+        <v>113</v>
+      </c>
+      <c r="D53" t="s">
+        <v>83</v>
+      </c>
+      <c r="E53">
+        <v>6</v>
+      </c>
+      <c r="F53">
+        <v>15</v>
+      </c>
+      <c r="G53">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>88</v>
+      </c>
+      <c r="C54" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" t="s">
+        <v>83</v>
+      </c>
+      <c r="E54">
+        <v>7</v>
+      </c>
+      <c r="F54">
+        <v>13</v>
+      </c>
+      <c r="G54">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>184</v>
+      </c>
+      <c r="C55" t="s">
+        <v>185</v>
+      </c>
+      <c r="D55" t="s">
+        <v>178</v>
+      </c>
+      <c r="E55">
+        <v>6</v>
+      </c>
+      <c r="F55">
+        <v>11</v>
+      </c>
+      <c r="G55">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>270</v>
+      </c>
+      <c r="C56" t="s">
+        <v>271</v>
+      </c>
+      <c r="D56" t="s">
+        <v>263</v>
+      </c>
+      <c r="E56">
+        <v>5</v>
+      </c>
+      <c r="F56">
+        <v>12</v>
+      </c>
+      <c r="G56">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57">
+        <v>6</v>
+      </c>
+      <c r="F57">
+        <v>13</v>
+      </c>
+      <c r="G57">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>89</v>
+      </c>
+      <c r="C58" t="s">
+        <v>90</v>
+      </c>
+      <c r="D58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E58">
+        <v>7</v>
+      </c>
+      <c r="F58">
+        <v>13</v>
+      </c>
+      <c r="G58">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>183</v>
+      </c>
+      <c r="C59" t="s">
+        <v>77</v>
+      </c>
+      <c r="D59" t="s">
+        <v>178</v>
+      </c>
+      <c r="E59">
+        <v>7</v>
+      </c>
+      <c r="F59">
+        <v>13</v>
+      </c>
+      <c r="G59">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>243</v>
+      </c>
+      <c r="C60" t="s">
+        <v>242</v>
+      </c>
+      <c r="D60" t="s">
+        <v>227</v>
+      </c>
+      <c r="E60">
+        <v>6</v>
+      </c>
+      <c r="F60">
+        <v>12</v>
+      </c>
+      <c r="G60">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>72</v>
+      </c>
+      <c r="C61" t="s">
+        <v>73</v>
+      </c>
+      <c r="D61" t="s">
+        <v>68</v>
+      </c>
+      <c r="E61">
+        <v>8</v>
+      </c>
+      <c r="F61">
+        <v>14</v>
+      </c>
+      <c r="G61">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>176</v>
+      </c>
+      <c r="C62" t="s">
+        <v>177</v>
+      </c>
+      <c r="D62" t="s">
+        <v>171</v>
+      </c>
+      <c r="E62">
+        <v>4</v>
+      </c>
+      <c r="F62">
+        <v>11</v>
+      </c>
+      <c r="G62">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>52</v>
+      </c>
+      <c r="C63" t="s">
+        <v>53</v>
+      </c>
+      <c r="D63" t="s">
+        <v>51</v>
+      </c>
+      <c r="E63">
+        <v>7</v>
+      </c>
+      <c r="F63">
+        <v>15</v>
+      </c>
+      <c r="G63">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>130</v>
+      </c>
+      <c r="C64" t="s">
+        <v>131</v>
+      </c>
+      <c r="D64" t="s">
+        <v>119</v>
+      </c>
+      <c r="E64">
+        <v>6</v>
+      </c>
+      <c r="F64">
+        <v>14</v>
+      </c>
+      <c r="G64">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>276</v>
+      </c>
+      <c r="C65" t="s">
+        <v>277</v>
+      </c>
+      <c r="D65" t="s">
+        <v>263</v>
+      </c>
+      <c r="E65">
+        <v>8</v>
+      </c>
+      <c r="F65">
+        <v>14</v>
+      </c>
+      <c r="G65">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>224</v>
+      </c>
+      <c r="C66" t="s">
+        <v>225</v>
+      </c>
+      <c r="D66" t="s">
+        <v>210</v>
+      </c>
+      <c r="E66">
+        <v>7</v>
+      </c>
+      <c r="F66">
+        <v>14</v>
+      </c>
+      <c r="G66">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>143</v>
+      </c>
+      <c r="C67" t="s">
+        <v>144</v>
+      </c>
+      <c r="D67" t="s">
+        <v>141</v>
+      </c>
+      <c r="E67">
+        <v>4</v>
+      </c>
+      <c r="F67">
+        <v>11</v>
+      </c>
+      <c r="G67">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>109</v>
+      </c>
+      <c r="C68" t="s">
+        <v>91</v>
+      </c>
+      <c r="D68" t="s">
+        <v>83</v>
+      </c>
+      <c r="E68">
+        <v>6</v>
+      </c>
+      <c r="F68">
+        <v>13</v>
+      </c>
+      <c r="G68">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>13</v>
+      </c>
+      <c r="C69" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69" t="s">
+        <v>17</v>
+      </c>
+      <c r="E69">
+        <v>6</v>
+      </c>
+      <c r="F69">
+        <v>12</v>
+      </c>
+      <c r="G69">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70">
+        <v>6</v>
+      </c>
+      <c r="F70">
+        <v>13</v>
+      </c>
+      <c r="G70">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>146</v>
+      </c>
+      <c r="C71" t="s">
+        <v>147</v>
+      </c>
+      <c r="D71" t="s">
+        <v>141</v>
+      </c>
+      <c r="E71">
+        <v>4</v>
+      </c>
+      <c r="F71">
+        <v>10</v>
+      </c>
+      <c r="G71">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>20</v>
+      </c>
+      <c r="C72" t="s">
+        <v>21</v>
+      </c>
+      <c r="D72" t="s">
+        <v>28</v>
+      </c>
+      <c r="E72">
+        <v>3</v>
+      </c>
+      <c r="F72">
+        <v>13</v>
+      </c>
+      <c r="G72">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" t="s">
+        <v>25</v>
+      </c>
+      <c r="D73" t="s">
+        <v>28</v>
+      </c>
+      <c r="E73">
+        <v>4</v>
+      </c>
+      <c r="F73">
+        <v>14</v>
+      </c>
+      <c r="G73">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>207</v>
+      </c>
+      <c r="C74" t="s">
+        <v>208</v>
+      </c>
+      <c r="D74" t="s">
+        <v>202</v>
+      </c>
+      <c r="E74">
+        <v>3</v>
+      </c>
+      <c r="F74">
+        <v>7</v>
+      </c>
+      <c r="G74">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>200</v>
+      </c>
+      <c r="C75" t="s">
+        <v>189</v>
+      </c>
+      <c r="D75" t="s">
+        <v>188</v>
+      </c>
+      <c r="E75">
+        <v>9</v>
+      </c>
+      <c r="F75">
+        <v>15</v>
+      </c>
+      <c r="G75">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>197</v>
+      </c>
+      <c r="C76" t="s">
+        <v>189</v>
+      </c>
+      <c r="D76" t="s">
+        <v>188</v>
+      </c>
+      <c r="E76">
+        <v>7</v>
+      </c>
+      <c r="F76">
+        <v>15</v>
+      </c>
+      <c r="G76">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>166</v>
+      </c>
+      <c r="C77" t="s">
+        <v>35</v>
+      </c>
+      <c r="D77" t="s">
+        <v>161</v>
+      </c>
+      <c r="E77">
+        <v>9</v>
+      </c>
+      <c r="F77">
+        <v>15</v>
+      </c>
+      <c r="G77">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>120</v>
+      </c>
+      <c r="C78" t="s">
+        <v>121</v>
+      </c>
+      <c r="D78" t="s">
+        <v>119</v>
+      </c>
+      <c r="E78">
+        <v>5</v>
+      </c>
+      <c r="F78">
+        <v>13</v>
+      </c>
+      <c r="G78">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>215</v>
+      </c>
+      <c r="C79" t="s">
+        <v>216</v>
+      </c>
+      <c r="D79" t="s">
+        <v>210</v>
+      </c>
+      <c r="E79">
+        <v>3</v>
+      </c>
+      <c r="F79">
+        <v>10</v>
+      </c>
+      <c r="G79">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>38</v>
+      </c>
+      <c r="C80" t="s">
+        <v>39</v>
+      </c>
+      <c r="D80" t="s">
+        <v>29</v>
+      </c>
+      <c r="E80">
+        <v>5</v>
+      </c>
+      <c r="F80">
+        <v>13</v>
+      </c>
+      <c r="G80">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>56</v>
+      </c>
+      <c r="C81" t="s">
+        <v>57</v>
+      </c>
+      <c r="D81" t="s">
+        <v>51</v>
+      </c>
+      <c r="E81">
+        <v>6</v>
+      </c>
+      <c r="F81">
+        <v>13</v>
+      </c>
+      <c r="G81">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>247</v>
+      </c>
+      <c r="C82" t="s">
+        <v>248</v>
+      </c>
+      <c r="D82" t="s">
+        <v>245</v>
+      </c>
+      <c r="E82">
+        <v>7</v>
+      </c>
+      <c r="F82">
+        <v>15</v>
+      </c>
+      <c r="G82">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>162</v>
+      </c>
+      <c r="C83" t="s">
+        <v>163</v>
+      </c>
+      <c r="D83" t="s">
+        <v>161</v>
+      </c>
+      <c r="E83">
+        <v>8</v>
+      </c>
+      <c r="F83">
+        <v>14</v>
+      </c>
+      <c r="G83">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>47</v>
+      </c>
+      <c r="C84" t="s">
+        <v>48</v>
+      </c>
+      <c r="D84" t="s">
+        <v>40</v>
+      </c>
+      <c r="E84">
+        <v>5</v>
+      </c>
+      <c r="F84">
+        <v>12</v>
+      </c>
+      <c r="G84">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>272</v>
+      </c>
+      <c r="C85" t="s">
+        <v>273</v>
+      </c>
+      <c r="D85" t="s">
+        <v>263</v>
+      </c>
+      <c r="E85">
+        <v>5</v>
+      </c>
+      <c r="F85">
+        <v>11</v>
+      </c>
+      <c r="G85">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>76</v>
+      </c>
+      <c r="C86" t="s">
+        <v>77</v>
+      </c>
+      <c r="D86" t="s">
+        <v>68</v>
+      </c>
+      <c r="E86">
+        <v>7</v>
+      </c>
+      <c r="F86">
+        <v>13</v>
+      </c>
+      <c r="G86">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>150</v>
+      </c>
+      <c r="C87" t="s">
+        <v>151</v>
+      </c>
+      <c r="D87" t="s">
+        <v>141</v>
+      </c>
+      <c r="E87">
+        <v>8</v>
+      </c>
+      <c r="F87">
+        <v>15</v>
+      </c>
+      <c r="G87">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>220</v>
+      </c>
+      <c r="C88" t="s">
+        <v>21</v>
+      </c>
+      <c r="D88" t="s">
+        <v>210</v>
+      </c>
+      <c r="E88">
+        <v>7</v>
+      </c>
+      <c r="F88">
+        <v>13</v>
+      </c>
+      <c r="G88">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>92</v>
+      </c>
+      <c r="C89" t="s">
+        <v>114</v>
+      </c>
+      <c r="D89" t="s">
+        <v>83</v>
+      </c>
+      <c r="E89">
+        <v>6</v>
+      </c>
+      <c r="F89">
+        <v>13</v>
+      </c>
+      <c r="G89">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>209</v>
+      </c>
+      <c r="C90" t="s">
+        <v>50</v>
+      </c>
+      <c r="D90" t="s">
+        <v>202</v>
+      </c>
+      <c r="E90">
+        <v>5</v>
+      </c>
+      <c r="F90">
+        <v>11</v>
+      </c>
+      <c r="G90">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>211</v>
+      </c>
+      <c r="C91" t="s">
+        <v>212</v>
+      </c>
+      <c r="D91" t="s">
+        <v>210</v>
+      </c>
+      <c r="E91">
+        <v>7</v>
+      </c>
+      <c r="F91">
+        <v>13</v>
+      </c>
+      <c r="G91">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>142</v>
+      </c>
+      <c r="C92" t="s">
+        <v>159</v>
+      </c>
+      <c r="D92" t="s">
+        <v>141</v>
+      </c>
+      <c r="E92">
+        <v>5</v>
+      </c>
+      <c r="F92">
+        <v>12</v>
+      </c>
+      <c r="G92">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>218</v>
+      </c>
+      <c r="C93" t="s">
+        <v>219</v>
+      </c>
+      <c r="D93" t="s">
+        <v>210</v>
+      </c>
+      <c r="E93">
+        <v>7</v>
+      </c>
+      <c r="F93">
+        <v>13</v>
+      </c>
+      <c r="G93">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>265</v>
+      </c>
+      <c r="C94" t="s">
+        <v>50</v>
+      </c>
+      <c r="D94" t="s">
+        <v>263</v>
+      </c>
+      <c r="E94">
+        <v>5</v>
+      </c>
+      <c r="F94">
+        <v>13</v>
+      </c>
+      <c r="G94">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>93</v>
+      </c>
+      <c r="C95" t="s">
+        <v>94</v>
+      </c>
+      <c r="D95" t="s">
+        <v>83</v>
+      </c>
+      <c r="E95">
+        <v>4</v>
+      </c>
+      <c r="F95">
+        <v>12</v>
+      </c>
+      <c r="G95">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>99</v>
+      </c>
+      <c r="C96" t="s">
+        <v>100</v>
+      </c>
+      <c r="D96" t="s">
+        <v>83</v>
+      </c>
+      <c r="E96">
+        <v>8</v>
+      </c>
+      <c r="F96">
+        <v>14</v>
+      </c>
+      <c r="G96">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>95</v>
+      </c>
+      <c r="C97" t="s">
+        <v>96</v>
+      </c>
+      <c r="D97" t="s">
+        <v>83</v>
+      </c>
+      <c r="E97">
+        <v>7</v>
+      </c>
+      <c r="F97">
+        <v>13</v>
+      </c>
+      <c r="G97">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>41</v>
+      </c>
+      <c r="C98" t="s">
+        <v>42</v>
+      </c>
+      <c r="D98" t="s">
+        <v>40</v>
+      </c>
+      <c r="E98">
+        <v>4</v>
+      </c>
+      <c r="F98">
+        <v>14</v>
+      </c>
+      <c r="G98">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>157</v>
+      </c>
+      <c r="C99" t="s">
+        <v>158</v>
+      </c>
+      <c r="D99" t="s">
+        <v>141</v>
+      </c>
+      <c r="E99">
+        <v>8</v>
+      </c>
+      <c r="F99">
+        <v>15</v>
+      </c>
+      <c r="G99">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>246</v>
+      </c>
+      <c r="C100" t="s">
+        <v>262</v>
+      </c>
+      <c r="D100" t="s">
+        <v>245</v>
+      </c>
+      <c r="E100">
+        <v>6</v>
+      </c>
+      <c r="F100">
+        <v>12</v>
+      </c>
+      <c r="G100">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>169</v>
+      </c>
+      <c r="C101" t="s">
+        <v>170</v>
+      </c>
+      <c r="D101" t="s">
+        <v>161</v>
+      </c>
+      <c r="E101">
+        <v>6</v>
+      </c>
+      <c r="F101">
+        <v>14</v>
+      </c>
+      <c r="G101">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>251</v>
+      </c>
+      <c r="C102" t="s">
+        <v>252</v>
+      </c>
+      <c r="D102" t="s">
+        <v>245</v>
+      </c>
+      <c r="E102">
+        <v>9</v>
+      </c>
+      <c r="F102">
+        <v>15</v>
+      </c>
+      <c r="G102">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>71</v>
+      </c>
+      <c r="C103" t="s">
+        <v>31</v>
+      </c>
+      <c r="D103" t="s">
+        <v>68</v>
+      </c>
+      <c r="E103">
+        <v>8</v>
+      </c>
+      <c r="F103">
+        <v>15</v>
+      </c>
+      <c r="G103">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>213</v>
+      </c>
+      <c r="C104" t="s">
+        <v>214</v>
+      </c>
+      <c r="D104" t="s">
+        <v>210</v>
+      </c>
+      <c r="E104">
+        <v>4</v>
+      </c>
+      <c r="F104">
+        <v>11</v>
+      </c>
+      <c r="G104">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>259</v>
+      </c>
+      <c r="C105" t="s">
+        <v>260</v>
+      </c>
+      <c r="D105" t="s">
+        <v>245</v>
+      </c>
+      <c r="E105">
+        <v>6</v>
+      </c>
+      <c r="F105">
+        <v>13</v>
+      </c>
+      <c r="G105">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>126</v>
+      </c>
+      <c r="C106" t="s">
+        <v>127</v>
+      </c>
+      <c r="D106" t="s">
+        <v>119</v>
+      </c>
+      <c r="E106">
+        <v>3</v>
+      </c>
+      <c r="F106">
+        <v>11</v>
+      </c>
+      <c r="G106">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>136</v>
+      </c>
+      <c r="C107" t="s">
+        <v>103</v>
+      </c>
+      <c r="D107" t="s">
+        <v>119</v>
+      </c>
+      <c r="E107">
+        <v>8</v>
+      </c>
+      <c r="F107">
+        <v>15</v>
+      </c>
+      <c r="G107">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>253</v>
+      </c>
+      <c r="C108" t="s">
+        <v>254</v>
+      </c>
+      <c r="D108" t="s">
+        <v>245</v>
+      </c>
+      <c r="E108">
+        <v>7</v>
+      </c>
+      <c r="F108">
+        <v>13</v>
+      </c>
+      <c r="G108">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>278</v>
+      </c>
+      <c r="C109" t="s">
+        <v>279</v>
+      </c>
+      <c r="D109" t="s">
+        <v>263</v>
+      </c>
+      <c r="E109">
+        <v>4</v>
+      </c>
+      <c r="F109">
+        <v>11</v>
+      </c>
+      <c r="G109">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>79</v>
+      </c>
+      <c r="C110" t="s">
+        <v>80</v>
+      </c>
+      <c r="D110" t="s">
+        <v>68</v>
+      </c>
+      <c r="E110">
+        <v>4</v>
+      </c>
+      <c r="F110">
+        <v>12</v>
+      </c>
+      <c r="G110">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>124</v>
+      </c>
+      <c r="C111" t="s">
+        <v>125</v>
+      </c>
+      <c r="D111" t="s">
+        <v>119</v>
+      </c>
+      <c r="E111">
+        <v>6</v>
+      </c>
+      <c r="F111">
+        <v>13</v>
+      </c>
+      <c r="G111">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>54</v>
+      </c>
+      <c r="C112" t="s">
+        <v>55</v>
+      </c>
+      <c r="D112" t="s">
+        <v>51</v>
+      </c>
+      <c r="E112">
+        <v>5</v>
+      </c>
+      <c r="F112">
+        <v>13</v>
+      </c>
+      <c r="G112">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>66</v>
+      </c>
+      <c r="C113" t="s">
+        <v>67</v>
+      </c>
+      <c r="D113" t="s">
+        <v>51</v>
+      </c>
+      <c r="E113">
+        <v>7</v>
+      </c>
+      <c r="F113">
+        <v>14</v>
+      </c>
+      <c r="G113">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>145</v>
+      </c>
+      <c r="C114" t="s">
+        <v>55</v>
+      </c>
+      <c r="D114" t="s">
+        <v>141</v>
+      </c>
+      <c r="E114">
+        <v>6</v>
+      </c>
+      <c r="F114">
+        <v>13</v>
+      </c>
+      <c r="G114">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>148</v>
+      </c>
+      <c r="C115" t="s">
+        <v>149</v>
+      </c>
+      <c r="D115" t="s">
+        <v>141</v>
+      </c>
+      <c r="E115">
+        <v>5</v>
+      </c>
+      <c r="F115">
+        <v>11</v>
+      </c>
+      <c r="G115">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>97</v>
+      </c>
+      <c r="C116" t="s">
+        <v>115</v>
+      </c>
+      <c r="D116" t="s">
+        <v>83</v>
+      </c>
+      <c r="E116">
+        <v>7</v>
+      </c>
+      <c r="F116">
+        <v>14</v>
+      </c>
+      <c r="G116">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>98</v>
+      </c>
+      <c r="C117" t="s">
+        <v>116</v>
+      </c>
+      <c r="D117" t="s">
+        <v>83</v>
+      </c>
+      <c r="E117">
+        <v>3</v>
+      </c>
+      <c r="F117">
+        <v>10</v>
+      </c>
+      <c r="G117">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>137</v>
+      </c>
+      <c r="C118" t="s">
+        <v>138</v>
+      </c>
+      <c r="D118" t="s">
+        <v>119</v>
+      </c>
+      <c r="E118">
+        <v>4</v>
+      </c>
+      <c r="F118">
+        <v>12</v>
+      </c>
+      <c r="G118">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>205</v>
+      </c>
+      <c r="C119" t="s">
+        <v>204</v>
+      </c>
+      <c r="D119" t="s">
+        <v>202</v>
+      </c>
+      <c r="E119">
+        <v>4</v>
+      </c>
+      <c r="F119">
+        <v>7</v>
+      </c>
+      <c r="G119">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>240</v>
+      </c>
+      <c r="C120" t="s">
+        <v>241</v>
+      </c>
+      <c r="D120" t="s">
+        <v>227</v>
+      </c>
+      <c r="E120">
+        <v>3</v>
+      </c>
+      <c r="F120">
+        <v>10</v>
+      </c>
+      <c r="G120">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>234</v>
+      </c>
+      <c r="C121" t="s">
+        <v>125</v>
+      </c>
+      <c r="D121" t="s">
+        <v>227</v>
+      </c>
+      <c r="E121">
+        <v>8</v>
+      </c>
+      <c r="F121">
+        <v>15</v>
+      </c>
+      <c r="G121">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>226</v>
+      </c>
+      <c r="C122" t="s">
+        <v>223</v>
+      </c>
+      <c r="D122" t="s">
+        <v>210</v>
+      </c>
+      <c r="E122">
+        <v>7</v>
+      </c>
+      <c r="F122">
+        <v>14</v>
+      </c>
+      <c r="G122">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>22</v>
+      </c>
+      <c r="C123" t="s">
+        <v>23</v>
+      </c>
+      <c r="D123" t="s">
+        <v>28</v>
+      </c>
+      <c r="E123">
+        <v>8</v>
+      </c>
+      <c r="F123">
+        <v>15</v>
+      </c>
+      <c r="G123">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>232</v>
+      </c>
+      <c r="C124" t="s">
+        <v>233</v>
+      </c>
+      <c r="D124" t="s">
+        <v>227</v>
+      </c>
+      <c r="E124">
+        <v>8</v>
+      </c>
+      <c r="F124">
+        <v>14</v>
+      </c>
+      <c r="G124">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>167</v>
+      </c>
+      <c r="C125" t="s">
+        <v>168</v>
+      </c>
+      <c r="D125" t="s">
+        <v>161</v>
+      </c>
+      <c r="E125">
+        <v>8</v>
+      </c>
+      <c r="F125">
+        <v>14</v>
+      </c>
+      <c r="G125">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>128</v>
+      </c>
+      <c r="C126" t="s">
+        <v>129</v>
+      </c>
+      <c r="D126" t="s">
+        <v>119</v>
+      </c>
+      <c r="E126">
+        <v>7</v>
+      </c>
+      <c r="F126">
+        <v>14</v>
+      </c>
+      <c r="G126">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>228</v>
+      </c>
+      <c r="C127" t="s">
+        <v>229</v>
+      </c>
+      <c r="D127" t="s">
+        <v>227</v>
+      </c>
+      <c r="E127">
+        <v>5</v>
+      </c>
+      <c r="F127">
+        <v>11</v>
+      </c>
+      <c r="G127">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>32</v>
+      </c>
+      <c r="C128" t="s">
+        <v>33</v>
+      </c>
+      <c r="D128" t="s">
+        <v>29</v>
+      </c>
+      <c r="E128">
+        <v>8</v>
+      </c>
+      <c r="F128">
+        <v>15</v>
+      </c>
+      <c r="G128">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>49</v>
+      </c>
+      <c r="C129" t="s">
+        <v>50</v>
+      </c>
+      <c r="D129" t="s">
+        <v>40</v>
+      </c>
+      <c r="E129">
+        <v>5</v>
+      </c>
+      <c r="F129">
+        <v>14</v>
+      </c>
+      <c r="G129">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>34</v>
+      </c>
+      <c r="C130" t="s">
+        <v>35</v>
+      </c>
+      <c r="D130" t="s">
+        <v>29</v>
+      </c>
+      <c r="E130">
+        <v>5</v>
+      </c>
+      <c r="F130">
+        <v>12</v>
+      </c>
+      <c r="G130">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>217</v>
+      </c>
+      <c r="C131" t="s">
+        <v>111</v>
+      </c>
+      <c r="D131" t="s">
+        <v>210</v>
+      </c>
+      <c r="E131">
+        <v>8</v>
+      </c>
+      <c r="F131">
+        <v>12</v>
+      </c>
+      <c r="G131">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>36</v>
+      </c>
+      <c r="C132" t="s">
+        <v>37</v>
+      </c>
+      <c r="D132" t="s">
+        <v>29</v>
+      </c>
+      <c r="E132">
+        <v>7</v>
+      </c>
+      <c r="F132">
+        <v>12</v>
+      </c>
+      <c r="G132">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>181</v>
+      </c>
+      <c r="C133" t="s">
+        <v>182</v>
+      </c>
+      <c r="D133" t="s">
+        <v>178</v>
+      </c>
+      <c r="E133">
+        <v>5</v>
+      </c>
+      <c r="F133">
+        <v>13</v>
+      </c>
+      <c r="G133">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>244</v>
+      </c>
+      <c r="C134" t="s">
+        <v>238</v>
+      </c>
+      <c r="D134" t="s">
+        <v>227</v>
+      </c>
+      <c r="E134">
+        <v>8</v>
+      </c>
+      <c r="F134">
+        <v>14</v>
+      </c>
+      <c r="G134">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>11</v>
+      </c>
+      <c r="C135" t="s">
+        <v>12</v>
+      </c>
+      <c r="D135" t="s">
+        <v>17</v>
+      </c>
+      <c r="E135">
+        <v>8</v>
+      </c>
+      <c r="F135">
+        <v>15</v>
+      </c>
+      <c r="G135">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>264</v>
+      </c>
+      <c r="C136" t="s">
+        <v>216</v>
+      </c>
+      <c r="D136" t="s">
+        <v>263</v>
+      </c>
+      <c r="E136">
+        <v>9</v>
+      </c>
+      <c r="F136">
+        <v>15</v>
+      </c>
+      <c r="G136">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>198</v>
+      </c>
+      <c r="C137" t="s">
+        <v>189</v>
+      </c>
+      <c r="D137" t="s">
+        <v>188</v>
+      </c>
+      <c r="E137">
+        <v>7</v>
+      </c>
+      <c r="F137">
+        <v>13</v>
+      </c>
+      <c r="G137">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>190</v>
+      </c>
+      <c r="C138" t="s">
+        <v>189</v>
+      </c>
+      <c r="D138" t="s">
+        <v>188</v>
+      </c>
+      <c r="E138">
+        <v>4</v>
+      </c>
+      <c r="F138">
+        <v>11</v>
+      </c>
+      <c r="G138">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>110</v>
+      </c>
+      <c r="C139" t="s">
+        <v>112</v>
+      </c>
+      <c r="D139" t="s">
+        <v>83</v>
+      </c>
+      <c r="E139">
+        <v>6</v>
+      </c>
+      <c r="F139">
+        <v>12</v>
+      </c>
+      <c r="G139">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>266</v>
+      </c>
+      <c r="C140" t="s">
+        <v>267</v>
+      </c>
+      <c r="D140" t="s">
+        <v>263</v>
+      </c>
+      <c r="E140">
+        <v>6</v>
+      </c>
+      <c r="F140">
+        <v>13</v>
+      </c>
+      <c r="G140">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>140</v>
+      </c>
+      <c r="C141" t="s">
+        <v>132</v>
+      </c>
+      <c r="D141" t="s">
+        <v>119</v>
+      </c>
+      <c r="E141">
+        <v>7</v>
+      </c>
+      <c r="F141">
+        <v>14</v>
+      </c>
+      <c r="G141">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>82</v>
+      </c>
+      <c r="C142" t="s">
+        <v>81</v>
+      </c>
+      <c r="D142" t="s">
+        <v>68</v>
+      </c>
+      <c r="E142">
+        <v>5</v>
+      </c>
+      <c r="F142">
+        <v>10</v>
+      </c>
+      <c r="G142">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>139</v>
+      </c>
+      <c r="C143" t="s">
+        <v>133</v>
+      </c>
+      <c r="D143" t="s">
+        <v>119</v>
+      </c>
+      <c r="E143">
+        <v>6</v>
+      </c>
+      <c r="F143">
+        <v>13</v>
+      </c>
+      <c r="G143">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C144" t="s">
+        <v>156</v>
+      </c>
+      <c r="D144" t="s">
+        <v>141</v>
+      </c>
+      <c r="E144">
+        <v>5</v>
+      </c>
+      <c r="F144">
+        <v>11</v>
+      </c>
+      <c r="G144">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H144" xr:uid="{F48EBC91-EB0A-4513-A427-E3024C547FB9}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H144">
+      <sortCondition ref="B1:B144"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/kalpa-songs.xlsx
+++ b/data/input/kalpa-songs.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aqua_\git\kalpa-selection\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A705EE-4D16-4D60-B193-B098CCB6C50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5891FE8-288E-4872-8054-D8E6DED1533E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17295" yWindow="2940" windowWidth="17235" windowHeight="11835" xr2:uid="{B18DF0BD-955E-4CF1-A738-32182884837D}"/>
+    <workbookView xWindow="-17295" yWindow="705" windowWidth="17235" windowHeight="14070" xr2:uid="{B18DF0BD-955E-4CF1-A738-32182884837D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$283</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="513">
   <si>
     <t>id</t>
   </si>
@@ -126,9 +126,6 @@
     <t>Aspid Cat</t>
   </si>
   <si>
-    <t>Dot-Line (short ver.)</t>
-  </si>
-  <si>
     <t>A-39 &amp; 沙包P &amp; ななひら</t>
   </si>
   <si>
@@ -263,9 +260,6 @@
     <t>Distorted Fate</t>
   </si>
   <si>
-    <t>Sakuzyo</t>
-  </si>
-  <si>
     <t>Rrhar'il</t>
   </si>
   <si>
@@ -318,9 +312,6 @@
   </si>
   <si>
     <t>GOODBOUNCE (Drunk Remix)</t>
-  </si>
-  <si>
-    <t>GOODRAGE (seatrus 海ックス)</t>
   </si>
   <si>
     <t>Halcyon (MRM REMIX)</t>
@@ -929,9 +920,6 @@
     <t>Vale</t>
   </si>
   <si>
-    <t>削除 (Sakuzyo)</t>
-  </si>
-  <si>
     <t>Capchii</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -978,21 +966,12 @@
     <t>BASTET</t>
   </si>
   <si>
-    <t xml:space="preserve"> Jehezukiel</t>
-  </si>
-  <si>
     <t>Boxel Adventure</t>
   </si>
   <si>
-    <t xml:space="preserve"> 7mai</t>
-  </si>
-  <si>
     <t>Satellite Adventure</t>
   </si>
   <si>
-    <t xml:space="preserve"> pan</t>
-  </si>
-  <si>
     <t xml:space="preserve">-Arkhēi- </t>
   </si>
   <si>
@@ -1056,6 +1035,1199 @@
   </si>
   <si>
     <t>Freaky Undulations ~Noble Knights of The Tune~</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>∀</t>
+  </si>
+  <si>
+    <t>¢orrupted ar¢hetype</t>
+  </si>
+  <si>
+    <t>Lauridsen &amp; VOiD</t>
+  </si>
+  <si>
+    <t>3.566×10^80m3</t>
+  </si>
+  <si>
+    <t>Apo11o program vs. Ice ft.朧-oboro-</t>
+  </si>
+  <si>
+    <t>420mb (Game Edit)</t>
+  </si>
+  <si>
+    <t>ariiol</t>
+  </si>
+  <si>
+    <t>Aci-L (Remaster)</t>
+  </si>
+  <si>
+    <t>Alice in Misanthrope -厭世アリス-</t>
+  </si>
+  <si>
+    <t>LeaF</t>
+  </si>
+  <si>
+    <t>Altale</t>
+  </si>
+  <si>
+    <t>削除(Sakuzyo)</t>
+  </si>
+  <si>
+    <t>ORIGINAL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Another Me</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D_AAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ars Cantate</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>rN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Aspera Noctis</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Aspera Noctis, Astra Lucis</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Kagetora. &amp; Ice feat. Scarlette</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>STORY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Astra Lucis</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ice feat. Scarlette</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Acataar ~ Reincarnation of Kalpa ~</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Scarlette a.k.a. CrYmson</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Äventyr</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rigël Theatre</t>
+  </si>
+  <si>
+    <t>Rigël Theatre</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bathin</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Team Grimoire</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Binary Wonderland</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7mai</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bloody Sisters♡Invasion</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ShrimpCats.(はぁち × 後藤涼輔)</t>
+    <rPh sb="18" eb="20">
+      <t>ゴトウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>タスク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Brain Power</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NOMA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Can U Feel It</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>siqlo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CANON (RYU Remix)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RYU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cat(ch) My♡Haxt!!!!!</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はぁち(Music：後藤涼輔)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Causality</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>kuro</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Chronostellar</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Salad Savior vs. U-Ruri</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>conflict</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>siromaru + cranky</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cross†Over feat. LyuU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HyuN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cutter</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EmoCosine</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dancer from the far east</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Halv</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DataErr0r</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cosmograph</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dear Farthest You</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>くるぶっこちゃん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Disorder feat. YURI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Diva of Avalon</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Connexio vs KONPEKi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Don't Never Around</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HAMA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Doppelganger</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LeaF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dot-Line feat. ななひら(short ver.)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Eldredth</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Nordius Dystancius (ZxNX &amp; Billium Moto)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Electric Comet</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Meram1n</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EMOTIONALL BRINGBACKK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Yu_Asahina VS orangentle</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Enceladus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Abel &amp; Hexacube</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Encore</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ZxNX &amp; Hiryur</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Entrance</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ice</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Eschatologu</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tetsh &amp; Scarlette</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ēvocator</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Evin a'k</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Faith of Eastward</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Reku Mochizuki</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>fallin' fallin' prod. INFX, Ella Jung, Limpid</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>kradness</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fantasia Sonata God Dance</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PYKAMIA vs. Sakuzyo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fantasia Sonata Imagination feat. Setsunann, 尋P</t>
+    <rPh sb="45" eb="46">
+      <t>タズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PYKAMIA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>felys -final remix-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>onoken</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Flutter Echo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cansol</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fragments</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sera Amagi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FREEDOM DiVE↓</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>xi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Frontierseekers Scarlette commissioned by </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고곰냥</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Scarlette</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FRIEND</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Giselle</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sobrem a.k.a. Widowmaker</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GOODRAGE (seatrus 海ックス)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GOODTEK (Sprint Remix)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Grabbing a Star</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Halcyon</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Happily Ever After</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HAZARD</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Limpid</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hello, Stranger</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LhoU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ignite</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Neutral Moon</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>immortality</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>INFiNiTE ENERZY -Overdoze-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>INSANE STRATEGY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Iris</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>a_hisa</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Kaleidosc0pe</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Kirakira Noel Story!!</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KiraKiraBoshi (pen Remix)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pan</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>L.Y.N.N.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>L2 -Reminiscence-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>la campanella scalatte</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Lapis (Remaster)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SHIKI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Libera me</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cranky</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Lightupperz!!</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Lost Eden feat. おくみずき</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dokuwaki</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Luminous Cosmos</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Nekoneet</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Miageta Sora wa Twin Star Datta </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mistilteinn</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LucaProject</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>My Heaven</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Jehezukiel</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NecronomicoN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KW9</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Neon tetra</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ginkiha feat. TEA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Nini</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テヅカ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Once again (VIP)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ophelia</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Oracle</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TQ ☆</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Orobas</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OSHIKOME☆HEAVEN'S COOKING</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>かゆき feat. ちょこ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Party Time!!</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Nekoribo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PATHFINDER</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>picotxlink</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>함께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그리는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>밤하늘의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이야기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> (Planetarium：Constellations)</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그리는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>밤하늘의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이야기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> prod. Scarlette (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Planetarium)</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Kyue &amp; kuripurin &amp; MYULee</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Psychometry</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PUPA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モリモリあつし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Raindrop</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rainy Waltz</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rapsodie fer za Cactuses (*'v'*)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Spiegel vs Ice</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Re:birth</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ああああ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Re:End of a Dream</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>uma vs. モリモリあつし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RE:UNION -Duo Blade Against-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ice vs. Morimori Atsushi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Red Bullet feat.はらもりよしな</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TAKIO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ЯeИ atus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>天束 feat.ぽめ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RESSiSTANCE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ぐるたみん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Revenant</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Revival of Kalpa</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>REVØCATE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RUSH prod.Scarlette</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>K.DaeHwan &amp; Scarlette</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sadachbia</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Seven Days of Genesis(Viollin：Scarlette)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Solstice</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>void (Mournfinale)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Soulwind</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sound Chimera</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Laur</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SPïKA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ST4RDUST☆XABER</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mono.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Star Sand Melts With Angel Tears</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Koki Sasaguchi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sunset Toybox</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テヅカ x Aoi feat.桃雛なの</t>
+    <rPh sb="15" eb="16">
+      <t>モモ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヒナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Swift Transaction</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PTB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Swing of the Bumblebee</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Symphony for the Revival</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tei-Tie-Breaker</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Haraki C-take</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>That Glacier</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Glancia</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>The Arcticlight</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>The Formula</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Junk</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>The Last Page</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ARForest</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>The Riot Reigns</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BLV3HAZUKI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Thunderstorm Road</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>yuudo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Time To Night Sky feat. Lee Yu Jin</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HyuN &amp; KLYDIX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Travel Begins</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Twilight Concerto(黄昏の協奏曲)</t>
+    <rPh sb="18" eb="20">
+      <t>タソガレ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>キョウソウキョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Valedict</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>void</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VALHALLA Melancholy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Valkyrie</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>World Brealer!! feat. BlueArpeggio</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ねむねむにゃんこパラダイス feat.Kyue</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>かゆき(Guiatr：deli.)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>もぺもぺ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>悪魔の御掌(Devil's Palm)</t>
+    <rPh sb="0" eb="2">
+      <t>アクマ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テノヒラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Kurokotei / 黒皇帝</t>
+    <rPh sb="12" eb="13">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>歌わなければ届かない、宇宙まで</t>
+    <rPh sb="0" eb="1">
+      <t>ウタ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>トド</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吹華咲乱(SuikaKyouran)</t>
+    <rPh sb="0" eb="1">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Now Field</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東方兔傳說 -SKY DEFENDER-</t>
+    <rPh sb="0" eb="2">
+      <t>トウホウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ウサギ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>デン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sctl</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>非日常スケッチブック (Unusual Sketchbook)</t>
+    <rPh sb="0" eb="3">
+      <t>ヒニチジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後藤 feat. Nayuta</t>
+    <rPh sb="0" eb="2">
+      <t>ゴトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>粉骨砕身カジノゥ</t>
+    <rPh sb="0" eb="4">
+      <t>フンコツサイシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ORIGINAL</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1063,7 +2235,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1123,6 +2295,27 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1146,11 +2339,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1487,11 +2683,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F48EBC91-EB0A-4513-A427-E3024C547FB9}">
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H283"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="30" customWidth="1"/>
+    <col min="1" max="1" width="5.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="27.125" customWidth="1"/>
     <col min="4" max="4" width="26.5" customWidth="1"/>
     <col min="5" max="8" width="10.625" customWidth="1"/>
     <col min="9" max="9" width="35" customWidth="1"/>
@@ -1528,22 +2724,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>193</v>
+        <v>276</v>
       </c>
       <c r="C2" t="s">
-        <v>189</v>
+        <v>277</v>
       </c>
       <c r="D2" t="s">
-        <v>188</v>
+        <v>287</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
@@ -1551,22 +2747,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>190</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>186</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>185</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>15</v>
       </c>
       <c r="G3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
@@ -1574,16 +2770,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C4" t="s">
-        <v>269</v>
+        <v>170</v>
       </c>
       <c r="D4" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F4">
         <v>13</v>
@@ -1597,13 +2793,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>278</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>279</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>287</v>
       </c>
       <c r="E5">
         <v>6</v>
@@ -1612,7 +2808,7 @@
         <v>13</v>
       </c>
       <c r="G5">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
@@ -1620,22 +2816,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>280</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>281</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>287</v>
       </c>
       <c r="E6">
         <v>6</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
@@ -1643,22 +2839,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="C7" t="s">
-        <v>223</v>
+        <v>299</v>
       </c>
       <c r="D7" t="s">
-        <v>245</v>
+        <v>295</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F7">
         <v>12</v>
       </c>
       <c r="G7">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
@@ -1666,19 +2862,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
+        <v>282</v>
+      </c>
+      <c r="C8">
+        <v>-45</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>287</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G8">
         <v>17</v>
@@ -1689,22 +2885,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G9">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
@@ -1712,22 +2908,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>283</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>284</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>287</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
@@ -1735,22 +2931,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>164</v>
+        <v>285</v>
       </c>
       <c r="C11" t="s">
-        <v>165</v>
+        <v>286</v>
       </c>
       <c r="D11" t="s">
-        <v>161</v>
+        <v>287</v>
       </c>
       <c r="E11">
         <v>6</v>
       </c>
       <c r="F11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
@@ -1758,19 +2954,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C12" t="s">
+        <v>262</v>
+      </c>
+      <c r="D12" t="s">
         <v>256</v>
       </c>
-      <c r="D12" t="s">
-        <v>245</v>
-      </c>
       <c r="E12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>17</v>
@@ -1781,22 +2977,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G13">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
@@ -1804,22 +3000,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>235</v>
+        <v>288</v>
       </c>
       <c r="C14" t="s">
-        <v>212</v>
+        <v>289</v>
       </c>
       <c r="D14" t="s">
-        <v>227</v>
+        <v>512</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G14">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
@@ -1827,22 +3023,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>186</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>187</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="E15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
@@ -1850,22 +3046,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>221</v>
+        <v>254</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>220</v>
       </c>
       <c r="D16" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
@@ -1873,22 +3069,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>194</v>
+        <v>290</v>
       </c>
       <c r="C17" t="s">
-        <v>189</v>
+        <v>291</v>
       </c>
       <c r="D17" t="s">
-        <v>188</v>
+        <v>295</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F17">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G17">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
@@ -1896,22 +3092,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>292</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>174</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>295</v>
       </c>
       <c r="E18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18">
         <v>15</v>
       </c>
       <c r="G18">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
@@ -1919,22 +3115,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>257</v>
+        <v>293</v>
       </c>
       <c r="C19" t="s">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="D19" t="s">
-        <v>245</v>
+        <v>295</v>
       </c>
       <c r="E19">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F19">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G19">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
@@ -1942,16 +3138,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F20">
         <v>12</v>
@@ -1965,13 +3161,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>296</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>297</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>295</v>
       </c>
       <c r="E21">
         <v>7</v>
@@ -1988,22 +3184,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>179</v>
+        <v>300</v>
       </c>
       <c r="C22" t="s">
-        <v>180</v>
+        <v>302</v>
       </c>
       <c r="D22" t="s">
-        <v>178</v>
+        <v>512</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G22">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
@@ -2011,22 +3207,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="C23" t="s">
-        <v>153</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G23">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
@@ -2034,22 +3230,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="E24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F24">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G24">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
@@ -2057,13 +3253,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="C25" t="s">
-        <v>231</v>
+        <v>162</v>
       </c>
       <c r="D25" t="s">
-        <v>227</v>
+        <v>158</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -2072,7 +3268,7 @@
         <v>13</v>
       </c>
       <c r="G25">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
@@ -2080,22 +3276,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="C26" t="s">
-        <v>237</v>
+        <v>414</v>
       </c>
       <c r="D26" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F26">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G26">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
@@ -2103,22 +3299,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>201</v>
+        <v>303</v>
       </c>
       <c r="C27" t="s">
-        <v>189</v>
+        <v>304</v>
       </c>
       <c r="D27" t="s">
-        <v>188</v>
+        <v>512</v>
       </c>
       <c r="E27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F27">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G27">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
@@ -2126,22 +3322,22 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="D28" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="E28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F28">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G28">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
@@ -2149,19 +3345,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>209</v>
       </c>
       <c r="D29" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="E29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G29">
         <v>16</v>
@@ -2172,22 +3368,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>172</v>
+        <v>305</v>
       </c>
       <c r="C30" t="s">
-        <v>173</v>
+        <v>306</v>
       </c>
       <c r="D30" t="s">
-        <v>171</v>
+        <v>512</v>
       </c>
       <c r="E30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F30">
         <v>12</v>
       </c>
       <c r="G30">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
@@ -2195,22 +3391,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C31" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D31" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F31">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G31">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
@@ -2218,22 +3414,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>218</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="E32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F32">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G32">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.4">
@@ -2241,22 +3437,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>174</v>
+        <v>307</v>
       </c>
       <c r="C33" t="s">
-        <v>175</v>
+        <v>308</v>
       </c>
       <c r="D33" t="s">
-        <v>171</v>
+        <v>295</v>
       </c>
       <c r="E33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F33">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G33">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.4">
@@ -2264,22 +3460,22 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>191</v>
       </c>
       <c r="C34" t="s">
-        <v>44</v>
+        <v>186</v>
       </c>
       <c r="D34" t="s">
-        <v>40</v>
+        <v>185</v>
       </c>
       <c r="E34">
         <v>6</v>
       </c>
       <c r="F34">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G34">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.4">
@@ -2287,19 +3483,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>154</v>
+        <v>57</v>
       </c>
       <c r="C35" t="s">
-        <v>155</v>
+        <v>58</v>
       </c>
       <c r="D35" t="s">
-        <v>141</v>
+        <v>50</v>
       </c>
       <c r="E35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F35">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G35">
         <v>17</v>
@@ -2310,22 +3506,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>74</v>
+        <v>252</v>
       </c>
       <c r="C36" t="s">
-        <v>75</v>
+        <v>306</v>
       </c>
       <c r="D36" t="s">
-        <v>68</v>
+        <v>241</v>
       </c>
       <c r="E36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F36">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G36">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.4">
@@ -2333,22 +3529,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>69</v>
+        <v>309</v>
       </c>
       <c r="C37" t="s">
-        <v>70</v>
+        <v>310</v>
       </c>
       <c r="D37" t="s">
-        <v>68</v>
+        <v>512</v>
       </c>
       <c r="E37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F37">
         <v>14</v>
       </c>
       <c r="G37">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.4">
@@ -2356,22 +3552,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="C38" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="D38" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G38">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.4">
@@ -2379,22 +3575,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>239</v>
+        <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>227</v>
+        <v>27</v>
       </c>
       <c r="E39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F39">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G39">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.4">
@@ -2402,22 +3598,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>64</v>
+        <v>176</v>
       </c>
       <c r="C40" t="s">
-        <v>65</v>
+        <v>177</v>
       </c>
       <c r="D40" t="s">
-        <v>51</v>
+        <v>175</v>
       </c>
       <c r="E40">
         <v>4</v>
       </c>
       <c r="F40">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G40">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.4">
@@ -2425,22 +3621,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41">
-        <v>-45</v>
+        <v>149</v>
+      </c>
+      <c r="C41" t="s">
+        <v>150</v>
       </c>
       <c r="D41" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="E41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F41">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G41">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.4">
@@ -2448,22 +3644,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>206</v>
+        <v>131</v>
       </c>
       <c r="C42" t="s">
-        <v>204</v>
+        <v>132</v>
       </c>
       <c r="D42" t="s">
-        <v>202</v>
+        <v>116</v>
       </c>
       <c r="E42">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F42">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G42">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.4">
@@ -2471,22 +3667,22 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>199</v>
+        <v>311</v>
       </c>
       <c r="C43" t="s">
-        <v>189</v>
+        <v>312</v>
       </c>
       <c r="D43" t="s">
-        <v>188</v>
+        <v>512</v>
       </c>
       <c r="E43">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F43">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G43">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.4">
@@ -2494,22 +3690,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>195</v>
+        <v>313</v>
       </c>
       <c r="C44" t="s">
-        <v>189</v>
+        <v>314</v>
       </c>
       <c r="D44" t="s">
-        <v>188</v>
+        <v>512</v>
       </c>
       <c r="E44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F44">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G44">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.4">
@@ -2517,22 +3713,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>249</v>
+        <v>315</v>
       </c>
       <c r="C45" t="s">
-        <v>117</v>
+        <v>316</v>
       </c>
       <c r="D45" t="s">
-        <v>245</v>
+        <v>512</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F45">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G45">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.4">
@@ -2540,22 +3736,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>203</v>
+        <v>317</v>
       </c>
       <c r="C46" t="s">
-        <v>204</v>
+        <v>318</v>
       </c>
       <c r="D46" t="s">
-        <v>202</v>
+        <v>295</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F46">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G46">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.4">
@@ -2563,22 +3759,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="C47" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="D47" t="s">
-        <v>263</v>
+        <v>512</v>
       </c>
       <c r="E47">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F47">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G47">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.4">
@@ -2586,22 +3782,22 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>281</v>
+        <v>227</v>
       </c>
       <c r="C48" t="s">
-        <v>280</v>
+        <v>228</v>
       </c>
       <c r="D48" t="s">
-        <v>263</v>
+        <v>224</v>
       </c>
       <c r="E48">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F48">
         <v>13</v>
       </c>
       <c r="G48">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.4">
@@ -2609,22 +3805,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>222</v>
-      </c>
-      <c r="C49">
-        <v>-45</v>
+        <v>233</v>
+      </c>
+      <c r="C49" t="s">
+        <v>234</v>
       </c>
       <c r="D49" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="E49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F49">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G49">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.4">
@@ -2632,19 +3828,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="C50" t="s">
-        <v>123</v>
+        <v>186</v>
       </c>
       <c r="D50" t="s">
-        <v>119</v>
+        <v>185</v>
       </c>
       <c r="E50">
         <v>7</v>
       </c>
       <c r="F50">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G50">
         <v>18</v>
@@ -2655,22 +3851,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>191</v>
+        <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="D51" t="s">
-        <v>188</v>
+        <v>67</v>
       </c>
       <c r="E51">
         <v>6</v>
       </c>
       <c r="F51">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G51">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.4">
@@ -2678,22 +3874,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>196</v>
+        <v>321</v>
       </c>
       <c r="C52" t="s">
-        <v>189</v>
+        <v>322</v>
       </c>
       <c r="D52" t="s">
-        <v>188</v>
+        <v>512</v>
       </c>
       <c r="E52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F52">
         <v>13</v>
       </c>
       <c r="G52">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.4">
@@ -2701,22 +3897,22 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>87</v>
+        <v>323</v>
       </c>
       <c r="C53" t="s">
-        <v>113</v>
+        <v>324</v>
       </c>
       <c r="D53" t="s">
-        <v>83</v>
+        <v>512</v>
       </c>
       <c r="E53">
         <v>6</v>
       </c>
       <c r="F53">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G53">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.4">
@@ -2724,22 +3920,22 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>88</v>
+        <v>246</v>
       </c>
       <c r="C54" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D54" t="s">
-        <v>83</v>
+        <v>241</v>
       </c>
       <c r="E54">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F54">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G54">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.4">
@@ -2747,22 +3943,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>184</v>
+        <v>325</v>
       </c>
       <c r="C55" t="s">
-        <v>185</v>
+        <v>326</v>
       </c>
       <c r="D55" t="s">
-        <v>178</v>
+        <v>512</v>
       </c>
       <c r="E55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F55">
         <v>11</v>
       </c>
       <c r="G55">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
@@ -2770,22 +3966,22 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>270</v>
+        <v>169</v>
       </c>
       <c r="C56" t="s">
-        <v>271</v>
+        <v>170</v>
       </c>
       <c r="D56" t="s">
-        <v>263</v>
+        <v>168</v>
       </c>
       <c r="E56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56">
         <v>12</v>
       </c>
       <c r="G56">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.4">
@@ -2793,22 +3989,22 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>15</v>
+        <v>189</v>
       </c>
       <c r="C57" t="s">
+        <v>186</v>
+      </c>
+      <c r="D57" t="s">
+        <v>185</v>
+      </c>
+      <c r="E57">
+        <v>5</v>
+      </c>
+      <c r="F57">
+        <v>11</v>
+      </c>
+      <c r="G57">
         <v>16</v>
-      </c>
-      <c r="D57" t="s">
-        <v>17</v>
-      </c>
-      <c r="E57">
-        <v>6</v>
-      </c>
-      <c r="F57">
-        <v>13</v>
-      </c>
-      <c r="G57">
-        <v>18</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.4">
@@ -2816,19 +4012,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>89</v>
+        <v>327</v>
       </c>
       <c r="C58" t="s">
-        <v>90</v>
+        <v>328</v>
       </c>
       <c r="D58" t="s">
-        <v>83</v>
+        <v>512</v>
       </c>
       <c r="E58">
         <v>7</v>
       </c>
       <c r="F58">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G58">
         <v>17</v>
@@ -2839,22 +4035,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>183</v>
+        <v>329</v>
       </c>
       <c r="C59" t="s">
-        <v>77</v>
+        <v>330</v>
       </c>
       <c r="D59" t="s">
-        <v>178</v>
+        <v>512</v>
       </c>
       <c r="E59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F59">
         <v>13</v>
       </c>
       <c r="G59">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.4">
@@ -2862,13 +4058,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>243</v>
+        <v>84</v>
       </c>
       <c r="C60" t="s">
-        <v>242</v>
+        <v>99</v>
       </c>
       <c r="D60" t="s">
-        <v>227</v>
+        <v>81</v>
       </c>
       <c r="E60">
         <v>6</v>
@@ -2877,7 +4073,7 @@
         <v>12</v>
       </c>
       <c r="G60">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.4">
@@ -2885,19 +4081,19 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="C61" t="s">
-        <v>73</v>
+        <v>172</v>
       </c>
       <c r="D61" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E61">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F61">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G61">
         <v>18</v>
@@ -2908,22 +4104,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>176</v>
+        <v>331</v>
       </c>
       <c r="C62" t="s">
-        <v>177</v>
+        <v>332</v>
       </c>
       <c r="D62" t="s">
-        <v>171</v>
+        <v>512</v>
       </c>
       <c r="E62">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F62">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G62">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
@@ -2931,22 +4127,22 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C63" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D63" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E63">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F63">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G63">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.4">
@@ -2954,19 +4150,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C64" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="D64" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="E64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G64">
         <v>17</v>
@@ -2977,19 +4173,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>276</v>
+        <v>72</v>
       </c>
       <c r="C65" t="s">
-        <v>277</v>
+        <v>73</v>
       </c>
       <c r="D65" t="s">
-        <v>263</v>
+        <v>67</v>
       </c>
       <c r="E65">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F65">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G65">
         <v>19</v>
@@ -3000,13 +4196,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>224</v>
+        <v>333</v>
       </c>
       <c r="C66" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="D66" t="s">
-        <v>210</v>
+        <v>512</v>
       </c>
       <c r="E66">
         <v>7</v>
@@ -3015,7 +4211,7 @@
         <v>14</v>
       </c>
       <c r="G66">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.4">
@@ -3023,22 +4219,22 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>143</v>
+        <v>68</v>
       </c>
       <c r="C67" t="s">
-        <v>144</v>
+        <v>286</v>
       </c>
       <c r="D67" t="s">
-        <v>141</v>
+        <v>67</v>
       </c>
       <c r="E67">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F67">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G67">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.4">
@@ -3046,22 +4242,22 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>109</v>
+        <v>334</v>
       </c>
       <c r="C68" t="s">
-        <v>91</v>
+        <v>335</v>
       </c>
       <c r="D68" t="s">
-        <v>83</v>
+        <v>512</v>
       </c>
       <c r="E68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F68">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G68">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.4">
@@ -3069,19 +4265,19 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>336</v>
+      </c>
+      <c r="C69" t="s">
+        <v>337</v>
+      </c>
+      <c r="D69" t="s">
+        <v>512</v>
+      </c>
+      <c r="E69">
+        <v>5</v>
+      </c>
+      <c r="F69">
         <v>13</v>
-      </c>
-      <c r="C69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D69" t="s">
-        <v>17</v>
-      </c>
-      <c r="E69">
-        <v>6</v>
-      </c>
-      <c r="F69">
-        <v>12</v>
       </c>
       <c r="G69">
         <v>17</v>
@@ -3092,22 +4288,22 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>338</v>
+      </c>
+      <c r="C70" t="s">
+        <v>339</v>
+      </c>
+      <c r="D70" t="s">
+        <v>512</v>
+      </c>
+      <c r="E70">
         <v>8</v>
       </c>
-      <c r="C70" t="s">
-        <v>9</v>
-      </c>
-      <c r="D70" t="s">
-        <v>17</v>
-      </c>
-      <c r="E70">
-        <v>6</v>
-      </c>
       <c r="F70">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G70">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.4">
@@ -3115,22 +4311,22 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>146</v>
+        <v>340</v>
       </c>
       <c r="C71" t="s">
-        <v>147</v>
+        <v>26</v>
       </c>
       <c r="D71" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="E71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F71">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G71">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.4">
@@ -3138,22 +4334,22 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>236</v>
+      </c>
+      <c r="C72" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" t="s">
+        <v>224</v>
+      </c>
+      <c r="E72">
+        <v>10</v>
+      </c>
+      <c r="F72">
+        <v>16</v>
+      </c>
+      <c r="G72">
         <v>20</v>
-      </c>
-      <c r="C72" t="s">
-        <v>21</v>
-      </c>
-      <c r="D72" t="s">
-        <v>28</v>
-      </c>
-      <c r="E72">
-        <v>3</v>
-      </c>
-      <c r="F72">
-        <v>13</v>
-      </c>
-      <c r="G72">
-        <v>17</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.4">
@@ -3161,22 +4357,22 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>24</v>
+        <v>341</v>
       </c>
       <c r="C73" t="s">
-        <v>25</v>
+        <v>342</v>
       </c>
       <c r="D73" t="s">
-        <v>28</v>
+        <v>512</v>
       </c>
       <c r="E73">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F73">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G73">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.4">
@@ -3184,22 +4380,22 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>207</v>
+        <v>343</v>
       </c>
       <c r="C74" t="s">
-        <v>208</v>
+        <v>344</v>
       </c>
       <c r="D74" t="s">
-        <v>202</v>
+        <v>295</v>
       </c>
       <c r="E74">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F74">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G74">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.4">
@@ -3207,22 +4403,22 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>200</v>
+        <v>345</v>
       </c>
       <c r="C75" t="s">
-        <v>189</v>
+        <v>346</v>
       </c>
       <c r="D75" t="s">
-        <v>188</v>
+        <v>512</v>
       </c>
       <c r="E75">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F75">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G75">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.4">
@@ -3230,22 +4426,22 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>197</v>
+        <v>347</v>
       </c>
       <c r="C76" t="s">
-        <v>189</v>
+        <v>348</v>
       </c>
       <c r="D76" t="s">
-        <v>188</v>
+        <v>512</v>
       </c>
       <c r="E76">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F76">
         <v>15</v>
       </c>
       <c r="G76">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.4">
@@ -3253,22 +4449,22 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>166</v>
+        <v>349</v>
       </c>
       <c r="C77" t="s">
-        <v>35</v>
+        <v>350</v>
       </c>
       <c r="D77" t="s">
-        <v>161</v>
+        <v>512</v>
       </c>
       <c r="E77">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F77">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G77">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.4">
@@ -3276,19 +4472,19 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>120</v>
+        <v>351</v>
       </c>
       <c r="C78" t="s">
-        <v>121</v>
+        <v>352</v>
       </c>
       <c r="D78" t="s">
-        <v>119</v>
+        <v>512</v>
       </c>
       <c r="E78">
         <v>5</v>
       </c>
       <c r="F78">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G78">
         <v>17</v>
@@ -3299,19 +4495,19 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>215</v>
+        <v>63</v>
       </c>
       <c r="C79" t="s">
-        <v>216</v>
+        <v>64</v>
       </c>
       <c r="D79" t="s">
-        <v>210</v>
+        <v>50</v>
       </c>
       <c r="E79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F79">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G79">
         <v>16</v>
@@ -3322,22 +4518,22 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
       <c r="C80" t="s">
-        <v>39</v>
+        <v>354</v>
       </c>
       <c r="D80" t="s">
-        <v>29</v>
+        <v>512</v>
       </c>
       <c r="E80">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F80">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G80">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.4">
@@ -3345,22 +4541,22 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>56</v>
+        <v>355</v>
       </c>
       <c r="C81" t="s">
-        <v>57</v>
+        <v>356</v>
       </c>
       <c r="D81" t="s">
-        <v>51</v>
+        <v>295</v>
       </c>
       <c r="E81">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F81">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G81">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.4">
@@ -3368,22 +4564,22 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>247</v>
-      </c>
-      <c r="C82" t="s">
-        <v>248</v>
+        <v>10</v>
+      </c>
+      <c r="C82">
+        <v>-45</v>
       </c>
       <c r="D82" t="s">
-        <v>245</v>
+        <v>17</v>
       </c>
       <c r="E82">
         <v>7</v>
       </c>
       <c r="F82">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G82">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.4">
@@ -3391,22 +4587,22 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>162</v>
+        <v>357</v>
       </c>
       <c r="C83" t="s">
-        <v>163</v>
+        <v>358</v>
       </c>
       <c r="D83" t="s">
-        <v>161</v>
+        <v>512</v>
       </c>
       <c r="E83">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F83">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G83">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.4">
@@ -3414,22 +4610,22 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>47</v>
+        <v>359</v>
       </c>
       <c r="C84" t="s">
-        <v>48</v>
+        <v>360</v>
       </c>
       <c r="D84" t="s">
-        <v>40</v>
+        <v>512</v>
       </c>
       <c r="E84">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F84">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G84">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.4">
@@ -3437,22 +4633,22 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>272</v>
+        <v>361</v>
       </c>
       <c r="C85" t="s">
-        <v>273</v>
+        <v>362</v>
       </c>
       <c r="D85" t="s">
-        <v>263</v>
+        <v>512</v>
       </c>
       <c r="E85">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F85">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G85">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.4">
@@ -3460,22 +4656,22 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>76</v>
+        <v>363</v>
       </c>
       <c r="C86" t="s">
-        <v>77</v>
+        <v>364</v>
       </c>
       <c r="D86" t="s">
-        <v>68</v>
+        <v>512</v>
       </c>
       <c r="E86">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F86">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G86">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.4">
@@ -3483,22 +4679,22 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="C87" t="s">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="D87" t="s">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="E87">
+        <v>4</v>
+      </c>
+      <c r="F87">
         <v>8</v>
       </c>
-      <c r="F87">
-        <v>15</v>
-      </c>
       <c r="G87">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.4">
@@ -3506,22 +4702,22 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>220</v>
+        <v>365</v>
       </c>
       <c r="C88" t="s">
-        <v>21</v>
+        <v>366</v>
       </c>
       <c r="D88" t="s">
-        <v>210</v>
+        <v>512</v>
       </c>
       <c r="E88">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F88">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G88">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.4">
@@ -3529,22 +4725,22 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>92</v>
+        <v>196</v>
       </c>
       <c r="C89" t="s">
-        <v>114</v>
+        <v>186</v>
       </c>
       <c r="D89" t="s">
-        <v>83</v>
+        <v>185</v>
       </c>
       <c r="E89">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F89">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G89">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.4">
@@ -3552,22 +4748,22 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="C90" t="s">
-        <v>50</v>
+        <v>186</v>
       </c>
       <c r="D90" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="E90">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F90">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G90">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.4">
@@ -3575,19 +4771,19 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="C91" t="s">
-        <v>212</v>
+        <v>114</v>
       </c>
       <c r="D91" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="E91">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F91">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G91">
         <v>17</v>
@@ -3598,13 +4794,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>142</v>
+        <v>367</v>
       </c>
       <c r="C92" t="s">
-        <v>159</v>
+        <v>368</v>
       </c>
       <c r="D92" t="s">
-        <v>141</v>
+        <v>295</v>
       </c>
       <c r="E92">
         <v>5</v>
@@ -3613,7 +4809,7 @@
         <v>12</v>
       </c>
       <c r="G92">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.4">
@@ -3621,22 +4817,22 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="C93" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="D93" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="E93">
+        <v>3</v>
+      </c>
+      <c r="F93">
+        <v>5</v>
+      </c>
+      <c r="G93">
         <v>7</v>
-      </c>
-      <c r="F93">
-        <v>13</v>
-      </c>
-      <c r="G93">
-        <v>18</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.4">
@@ -3644,22 +4840,22 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C94" t="s">
-        <v>50</v>
+        <v>268</v>
       </c>
       <c r="D94" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="E94">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F94">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G94">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.4">
@@ -3667,22 +4863,22 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>93</v>
+        <v>369</v>
       </c>
       <c r="C95" t="s">
-        <v>94</v>
+        <v>370</v>
       </c>
       <c r="D95" t="s">
-        <v>83</v>
+        <v>512</v>
       </c>
       <c r="E95">
         <v>4</v>
       </c>
       <c r="F95">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G95">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.4">
@@ -3690,22 +4886,22 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>99</v>
+        <v>274</v>
       </c>
       <c r="C96" t="s">
-        <v>100</v>
+        <v>273</v>
       </c>
       <c r="D96" t="s">
-        <v>83</v>
+        <v>256</v>
       </c>
       <c r="E96">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F96">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G96">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.4">
@@ -3713,22 +4909,22 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>95</v>
+        <v>371</v>
       </c>
       <c r="C97" t="s">
-        <v>96</v>
+        <v>372</v>
       </c>
       <c r="D97" t="s">
-        <v>83</v>
+        <v>512</v>
       </c>
       <c r="E97">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F97">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G97">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.4">
@@ -3736,22 +4932,22 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>41</v>
+        <v>375</v>
       </c>
       <c r="C98" t="s">
-        <v>42</v>
+        <v>289</v>
       </c>
       <c r="D98" t="s">
-        <v>40</v>
+        <v>512</v>
       </c>
       <c r="E98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F98">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G98">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.4">
@@ -3759,22 +4955,22 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>157</v>
+        <v>373</v>
       </c>
       <c r="C99" t="s">
-        <v>158</v>
+        <v>374</v>
       </c>
       <c r="D99" t="s">
-        <v>141</v>
+        <v>512</v>
       </c>
       <c r="E99">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F99">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G99">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.4">
@@ -3782,22 +4978,22 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>246</v>
-      </c>
-      <c r="C100" t="s">
-        <v>262</v>
+        <v>219</v>
+      </c>
+      <c r="C100">
+        <v>-45</v>
       </c>
       <c r="D100" t="s">
-        <v>245</v>
+        <v>207</v>
       </c>
       <c r="E100">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F100">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G100">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.4">
@@ -3805,22 +5001,22 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>169</v>
+        <v>119</v>
       </c>
       <c r="C101" t="s">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="D101" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="E101">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F101">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G101">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.4">
@@ -3828,22 +5024,22 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>251</v>
+        <v>188</v>
       </c>
       <c r="C102" t="s">
-        <v>252</v>
+        <v>186</v>
       </c>
       <c r="D102" t="s">
-        <v>245</v>
+        <v>185</v>
       </c>
       <c r="E102">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F102">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G102">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.4">
@@ -3851,19 +5047,19 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="C103" t="s">
-        <v>31</v>
+        <v>186</v>
       </c>
       <c r="D103" t="s">
-        <v>68</v>
+        <v>185</v>
       </c>
       <c r="E103">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F103">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G103">
         <v>18</v>
@@ -3874,22 +5070,22 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>213</v>
+        <v>376</v>
       </c>
       <c r="C104" t="s">
-        <v>214</v>
+        <v>377</v>
       </c>
       <c r="D104" t="s">
-        <v>210</v>
+        <v>512</v>
       </c>
       <c r="E104">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F104">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G104">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.4">
@@ -3897,22 +5093,22 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>259</v>
+        <v>85</v>
       </c>
       <c r="C105" t="s">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="D105" t="s">
-        <v>245</v>
+        <v>81</v>
       </c>
       <c r="E105">
         <v>6</v>
       </c>
       <c r="F105">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G105">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.4">
@@ -3920,22 +5116,22 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>126</v>
+        <v>378</v>
       </c>
       <c r="C106" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="D106" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="E106">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F106">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G106">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.4">
@@ -3943,22 +5139,22 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>136</v>
+        <v>379</v>
       </c>
       <c r="C107" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D107" t="s">
-        <v>119</v>
+        <v>512</v>
       </c>
       <c r="E107">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F107">
         <v>15</v>
       </c>
       <c r="G107">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.4">
@@ -3966,13 +5162,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>253</v>
+        <v>380</v>
       </c>
       <c r="C108" t="s">
-        <v>254</v>
+        <v>101</v>
       </c>
       <c r="D108" t="s">
-        <v>245</v>
+        <v>295</v>
       </c>
       <c r="E108">
         <v>7</v>
@@ -3989,16 +5185,16 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>278</v>
+        <v>181</v>
       </c>
       <c r="C109" t="s">
-        <v>279</v>
+        <v>182</v>
       </c>
       <c r="D109" t="s">
-        <v>263</v>
+        <v>175</v>
       </c>
       <c r="E109">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F109">
         <v>11</v>
@@ -4012,22 +5208,22 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>79</v>
+        <v>263</v>
       </c>
       <c r="C110" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="D110" t="s">
-        <v>68</v>
+        <v>256</v>
       </c>
       <c r="E110">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F110">
         <v>12</v>
       </c>
       <c r="G110">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.4">
@@ -4035,13 +5231,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="C111" t="s">
-        <v>125</v>
+        <v>16</v>
       </c>
       <c r="D111" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="E111">
         <v>6</v>
@@ -4050,7 +5246,7 @@
         <v>13</v>
       </c>
       <c r="G111">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.4">
@@ -4058,16 +5254,16 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>54</v>
+        <v>381</v>
       </c>
       <c r="C112" t="s">
-        <v>55</v>
+        <v>372</v>
       </c>
       <c r="D112" t="s">
-        <v>51</v>
+        <v>512</v>
       </c>
       <c r="E112">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F112">
         <v>13</v>
@@ -4081,19 +5277,19 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C113" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D113" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="E113">
         <v>7</v>
       </c>
       <c r="F113">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G113">
         <v>17</v>
@@ -4104,22 +5300,22 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>145</v>
+        <v>382</v>
       </c>
       <c r="C114" t="s">
-        <v>55</v>
+        <v>368</v>
       </c>
       <c r="D114" t="s">
-        <v>141</v>
+        <v>295</v>
       </c>
       <c r="E114">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F114">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G114">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.4">
@@ -4127,22 +5323,22 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="C115" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="D115" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="E115">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F115">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G115">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.4">
@@ -4150,22 +5346,22 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>97</v>
+        <v>383</v>
       </c>
       <c r="C116" t="s">
-        <v>115</v>
+        <v>384</v>
       </c>
       <c r="D116" t="s">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="E116">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F116">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G116">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.4">
@@ -4173,22 +5369,22 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>98</v>
+        <v>385</v>
       </c>
       <c r="C117" t="s">
-        <v>116</v>
+        <v>386</v>
       </c>
       <c r="D117" t="s">
-        <v>83</v>
+        <v>512</v>
       </c>
       <c r="E117">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F117">
         <v>10</v>
       </c>
       <c r="G117">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.4">
@@ -4196,22 +5392,22 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>137</v>
+        <v>239</v>
       </c>
       <c r="C118" t="s">
-        <v>138</v>
+        <v>238</v>
       </c>
       <c r="D118" t="s">
-        <v>119</v>
+        <v>224</v>
       </c>
       <c r="E118">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F118">
         <v>12</v>
       </c>
       <c r="G118">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.4">
@@ -4219,22 +5415,22 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>205</v>
+        <v>70</v>
       </c>
       <c r="C119" t="s">
-        <v>204</v>
+        <v>71</v>
       </c>
       <c r="D119" t="s">
-        <v>202</v>
+        <v>67</v>
       </c>
       <c r="E119">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F119">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G119">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.4">
@@ -4242,22 +5438,22 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>240</v>
+        <v>387</v>
       </c>
       <c r="C120" t="s">
-        <v>241</v>
+        <v>388</v>
       </c>
       <c r="D120" t="s">
-        <v>227</v>
+        <v>295</v>
       </c>
       <c r="E120">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F120">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G120">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.4">
@@ -4265,22 +5461,22 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>234</v>
+        <v>389</v>
       </c>
       <c r="C121" t="s">
-        <v>125</v>
+        <v>49</v>
       </c>
       <c r="D121" t="s">
-        <v>227</v>
+        <v>295</v>
       </c>
       <c r="E121">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F121">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G121">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.4">
@@ -4288,22 +5484,22 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>226</v>
+        <v>390</v>
       </c>
       <c r="C122" t="s">
-        <v>223</v>
+        <v>358</v>
       </c>
       <c r="D122" t="s">
-        <v>210</v>
+        <v>512</v>
       </c>
       <c r="E122">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F122">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G122">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.4">
@@ -4311,22 +5507,22 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>22</v>
+        <v>173</v>
       </c>
       <c r="C123" t="s">
-        <v>23</v>
+        <v>174</v>
       </c>
       <c r="D123" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E123">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F123">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G123">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.4">
@@ -4334,22 +5530,22 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>232</v>
+        <v>391</v>
       </c>
       <c r="C124" t="s">
-        <v>233</v>
+        <v>384</v>
       </c>
       <c r="D124" t="s">
-        <v>227</v>
+        <v>295</v>
       </c>
       <c r="E124">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F124">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G124">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.4">
@@ -4357,19 +5553,19 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>167</v>
+        <v>51</v>
       </c>
       <c r="C125" t="s">
-        <v>168</v>
+        <v>52</v>
       </c>
       <c r="D125" t="s">
-        <v>161</v>
+        <v>50</v>
       </c>
       <c r="E125">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F125">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G125">
         <v>17</v>
@@ -4380,22 +5576,22 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
+        <v>127</v>
+      </c>
+      <c r="C126" t="s">
         <v>128</v>
       </c>
-      <c r="C126" t="s">
-        <v>129</v>
-      </c>
       <c r="D126" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E126">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F126">
         <v>14</v>
       </c>
       <c r="G126">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.4">
@@ -4403,22 +5599,22 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>228</v>
+        <v>269</v>
       </c>
       <c r="C127" t="s">
-        <v>229</v>
+        <v>270</v>
       </c>
       <c r="D127" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="E127">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F127">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G127">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.4">
@@ -4426,22 +5622,22 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>32</v>
+        <v>392</v>
       </c>
       <c r="C128" t="s">
-        <v>33</v>
+        <v>393</v>
       </c>
       <c r="D128" t="s">
-        <v>29</v>
+        <v>512</v>
       </c>
       <c r="E128">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F128">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G128">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.4">
@@ -4449,16 +5645,16 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>49</v>
+        <v>394</v>
       </c>
       <c r="C129" t="s">
-        <v>50</v>
+        <v>328</v>
       </c>
       <c r="D129" t="s">
-        <v>40</v>
+        <v>512</v>
       </c>
       <c r="E129">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F129">
         <v>14</v>
@@ -4472,22 +5668,22 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>34</v>
+        <v>221</v>
       </c>
       <c r="C130" t="s">
-        <v>35</v>
+        <v>222</v>
       </c>
       <c r="D130" t="s">
-        <v>29</v>
+        <v>207</v>
       </c>
       <c r="E130">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F130">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G130">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.4">
@@ -4495,22 +5691,22 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>217</v>
+        <v>395</v>
       </c>
       <c r="C131" t="s">
-        <v>111</v>
+        <v>358</v>
       </c>
       <c r="D131" t="s">
-        <v>210</v>
+        <v>512</v>
       </c>
       <c r="E131">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F131">
         <v>12</v>
       </c>
       <c r="G131">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.4">
@@ -4518,16 +5714,16 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>36</v>
+        <v>396</v>
       </c>
       <c r="C132" t="s">
-        <v>37</v>
+        <v>397</v>
       </c>
       <c r="D132" t="s">
-        <v>29</v>
+        <v>512</v>
       </c>
       <c r="E132">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F132">
         <v>12</v>
@@ -4541,22 +5737,22 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="C133" t="s">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="D133" t="s">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="E133">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F133">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G133">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.4">
@@ -4564,22 +5760,22 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>244</v>
+        <v>398</v>
       </c>
       <c r="C134" t="s">
-        <v>238</v>
+        <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>227</v>
+        <v>295</v>
       </c>
       <c r="E134">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F134">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G134">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.4">
@@ -4587,22 +5783,22 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>11</v>
+        <v>399</v>
       </c>
       <c r="C135" t="s">
-        <v>12</v>
+        <v>352</v>
       </c>
       <c r="D135" t="s">
-        <v>17</v>
+        <v>512</v>
       </c>
       <c r="E135">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F135">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G135">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.4">
@@ -4610,22 +5806,22 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>264</v>
+        <v>400</v>
       </c>
       <c r="C136" t="s">
-        <v>216</v>
+        <v>49</v>
       </c>
       <c r="D136" t="s">
-        <v>263</v>
+        <v>512</v>
       </c>
       <c r="E136">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F136">
+        <v>11</v>
+      </c>
+      <c r="G136">
         <v>15</v>
-      </c>
-      <c r="G136">
-        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.4">
@@ -4633,16 +5829,16 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>198</v>
+        <v>106</v>
       </c>
       <c r="C137" t="s">
-        <v>189</v>
+        <v>88</v>
       </c>
       <c r="D137" t="s">
-        <v>188</v>
+        <v>81</v>
       </c>
       <c r="E137">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F137">
         <v>13</v>
@@ -4656,19 +5852,19 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>190</v>
+        <v>401</v>
       </c>
       <c r="C138" t="s">
-        <v>189</v>
+        <v>402</v>
       </c>
       <c r="D138" t="s">
-        <v>188</v>
+        <v>512</v>
       </c>
       <c r="E138">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F138">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G138">
         <v>16</v>
@@ -4679,13 +5875,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="C139" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D139" t="s">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="E139">
         <v>6</v>
@@ -4702,13 +5898,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>266</v>
+        <v>8</v>
       </c>
       <c r="C140" t="s">
-        <v>267</v>
+        <v>9</v>
       </c>
       <c r="D140" t="s">
-        <v>263</v>
+        <v>17</v>
       </c>
       <c r="E140">
         <v>6</v>
@@ -4725,19 +5921,19 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>140</v>
+        <v>403</v>
       </c>
       <c r="C141" t="s">
-        <v>132</v>
+        <v>404</v>
       </c>
       <c r="D141" t="s">
-        <v>119</v>
+        <v>512</v>
       </c>
       <c r="E141">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F141">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G141">
         <v>17</v>
@@ -4748,16 +5944,16 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="C142" t="s">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="D142" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="E142">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F142">
         <v>10</v>
@@ -4771,51 +5967,3248 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>139</v>
+        <v>405</v>
       </c>
       <c r="C143" t="s">
-        <v>133</v>
+        <v>358</v>
       </c>
       <c r="D143" t="s">
-        <v>119</v>
+        <v>512</v>
       </c>
       <c r="E143">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F143">
         <v>13</v>
       </c>
       <c r="G143">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A144">
         <v>143</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="B144" t="s">
+        <v>20</v>
+      </c>
+      <c r="C144" t="s">
+        <v>21</v>
+      </c>
+      <c r="D144" t="s">
+        <v>27</v>
+      </c>
+      <c r="E144">
+        <v>3</v>
+      </c>
+      <c r="F144">
+        <v>13</v>
+      </c>
+      <c r="G144">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>406</v>
+      </c>
+      <c r="C145" t="s">
+        <v>407</v>
+      </c>
+      <c r="D145" t="s">
+        <v>512</v>
+      </c>
+      <c r="E145">
+        <v>6</v>
+      </c>
+      <c r="F145">
+        <v>12</v>
+      </c>
+      <c r="G145">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>24</v>
+      </c>
+      <c r="C146" t="s">
+        <v>25</v>
+      </c>
+      <c r="D146" t="s">
+        <v>27</v>
+      </c>
+      <c r="E146">
+        <v>4</v>
+      </c>
+      <c r="F146">
+        <v>14</v>
+      </c>
+      <c r="G146">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>204</v>
+      </c>
+      <c r="C147" t="s">
+        <v>205</v>
+      </c>
+      <c r="D147" t="s">
+        <v>199</v>
+      </c>
+      <c r="E147">
+        <v>3</v>
+      </c>
+      <c r="F147">
+        <v>7</v>
+      </c>
+      <c r="G147">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>408</v>
+      </c>
+      <c r="C148" t="s">
+        <v>409</v>
+      </c>
+      <c r="D148" t="s">
+        <v>512</v>
+      </c>
+      <c r="E148">
+        <v>7</v>
+      </c>
+      <c r="F148">
+        <v>13</v>
+      </c>
+      <c r="G148">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>197</v>
+      </c>
+      <c r="C149" t="s">
+        <v>186</v>
+      </c>
+      <c r="D149" t="s">
+        <v>185</v>
+      </c>
+      <c r="E149">
+        <v>9</v>
+      </c>
+      <c r="F149">
+        <v>15</v>
+      </c>
+      <c r="G149">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>194</v>
+      </c>
+      <c r="C150" t="s">
+        <v>186</v>
+      </c>
+      <c r="D150" t="s">
+        <v>185</v>
+      </c>
+      <c r="E150">
+        <v>7</v>
+      </c>
+      <c r="F150">
+        <v>15</v>
+      </c>
+      <c r="G150">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>163</v>
+      </c>
+      <c r="C151" t="s">
+        <v>34</v>
+      </c>
+      <c r="D151" t="s">
+        <v>158</v>
+      </c>
+      <c r="E151">
+        <v>9</v>
+      </c>
+      <c r="F151">
+        <v>15</v>
+      </c>
+      <c r="G151">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>117</v>
+      </c>
+      <c r="C152" t="s">
+        <v>118</v>
+      </c>
+      <c r="D152" t="s">
+        <v>116</v>
+      </c>
+      <c r="E152">
+        <v>5</v>
+      </c>
+      <c r="F152">
+        <v>13</v>
+      </c>
+      <c r="G152">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>410</v>
+      </c>
+      <c r="C153" t="s">
+        <v>374</v>
+      </c>
+      <c r="D153" t="s">
+        <v>512</v>
+      </c>
+      <c r="E153">
+        <v>3</v>
+      </c>
+      <c r="F153">
+        <v>10</v>
+      </c>
+      <c r="G153">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>212</v>
+      </c>
+      <c r="C154" t="s">
+        <v>213</v>
+      </c>
+      <c r="D154" t="s">
+        <v>207</v>
+      </c>
+      <c r="E154">
+        <v>3</v>
+      </c>
+      <c r="F154">
+        <v>10</v>
+      </c>
+      <c r="G154">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>411</v>
+      </c>
+      <c r="C155" t="s">
+        <v>412</v>
+      </c>
+      <c r="D155" t="s">
+        <v>512</v>
+      </c>
+      <c r="E155">
+        <v>4</v>
+      </c>
+      <c r="F155">
+        <v>13</v>
+      </c>
+      <c r="G155">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>37</v>
+      </c>
+      <c r="C156" t="s">
+        <v>38</v>
+      </c>
+      <c r="D156" t="s">
+        <v>28</v>
+      </c>
+      <c r="E156">
+        <v>5</v>
+      </c>
+      <c r="F156">
+        <v>13</v>
+      </c>
+      <c r="G156">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>55</v>
+      </c>
+      <c r="C157" t="s">
+        <v>56</v>
+      </c>
+      <c r="D157" t="s">
+        <v>50</v>
+      </c>
+      <c r="E157">
+        <v>6</v>
+      </c>
+      <c r="F157">
+        <v>13</v>
+      </c>
+      <c r="G157">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" t="s">
+        <v>243</v>
+      </c>
+      <c r="C158" t="s">
+        <v>244</v>
+      </c>
+      <c r="D158" t="s">
+        <v>241</v>
+      </c>
+      <c r="E158">
+        <v>7</v>
+      </c>
+      <c r="F158">
+        <v>15</v>
+      </c>
+      <c r="G158">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159" t="s">
+        <v>413</v>
+      </c>
+      <c r="C159" t="s">
+        <v>414</v>
+      </c>
+      <c r="D159" t="s">
+        <v>295</v>
+      </c>
+      <c r="E159">
+        <v>6</v>
+      </c>
+      <c r="F159">
+        <v>12</v>
+      </c>
+      <c r="G159">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160" t="s">
+        <v>159</v>
+      </c>
+      <c r="C160" t="s">
         <v>160</v>
       </c>
-      <c r="C144" t="s">
+      <c r="D160" t="s">
+        <v>158</v>
+      </c>
+      <c r="E160">
+        <v>8</v>
+      </c>
+      <c r="F160">
+        <v>14</v>
+      </c>
+      <c r="G160">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161" t="s">
+        <v>415</v>
+      </c>
+      <c r="C161" t="s">
+        <v>416</v>
+      </c>
+      <c r="D161" t="s">
+        <v>512</v>
+      </c>
+      <c r="E161">
+        <v>7</v>
+      </c>
+      <c r="F161">
+        <v>14</v>
+      </c>
+      <c r="G161">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162" t="s">
+        <v>417</v>
+      </c>
+      <c r="C162" t="s">
+        <v>418</v>
+      </c>
+      <c r="D162" t="s">
+        <v>512</v>
+      </c>
+      <c r="E162">
+        <v>1</v>
+      </c>
+      <c r="F162">
+        <v>9</v>
+      </c>
+      <c r="G162">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163" t="s">
+        <v>46</v>
+      </c>
+      <c r="C163" t="s">
+        <v>47</v>
+      </c>
+      <c r="D163" t="s">
+        <v>39</v>
+      </c>
+      <c r="E163">
+        <v>5</v>
+      </c>
+      <c r="F163">
+        <v>12</v>
+      </c>
+      <c r="G163">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164" t="s">
+        <v>265</v>
+      </c>
+      <c r="C164" t="s">
+        <v>266</v>
+      </c>
+      <c r="D164" t="s">
+        <v>256</v>
+      </c>
+      <c r="E164">
+        <v>5</v>
+      </c>
+      <c r="F164">
+        <v>11</v>
+      </c>
+      <c r="G164">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165" t="s">
+        <v>419</v>
+      </c>
+      <c r="C165" t="s">
+        <v>420</v>
+      </c>
+      <c r="D165" t="s">
+        <v>512</v>
+      </c>
+      <c r="E165">
+        <v>6</v>
+      </c>
+      <c r="F165">
+        <v>11</v>
+      </c>
+      <c r="G165">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166" t="s">
+        <v>74</v>
+      </c>
+      <c r="C166" t="s">
+        <v>75</v>
+      </c>
+      <c r="D166" t="s">
+        <v>67</v>
+      </c>
+      <c r="E166">
+        <v>7</v>
+      </c>
+      <c r="F166">
+        <v>13</v>
+      </c>
+      <c r="G166">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167" t="s">
+        <v>147</v>
+      </c>
+      <c r="C167" t="s">
+        <v>148</v>
+      </c>
+      <c r="D167" t="s">
+        <v>138</v>
+      </c>
+      <c r="E167">
+        <v>8</v>
+      </c>
+      <c r="F167">
+        <v>15</v>
+      </c>
+      <c r="G167">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168" t="s">
+        <v>217</v>
+      </c>
+      <c r="C168" t="s">
+        <v>21</v>
+      </c>
+      <c r="D168" t="s">
+        <v>207</v>
+      </c>
+      <c r="E168">
+        <v>7</v>
+      </c>
+      <c r="F168">
+        <v>13</v>
+      </c>
+      <c r="G168">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169" t="s">
+        <v>421</v>
+      </c>
+      <c r="C169" t="s">
+        <v>368</v>
+      </c>
+      <c r="D169" t="s">
+        <v>512</v>
+      </c>
+      <c r="E169">
+        <v>9</v>
+      </c>
+      <c r="F169">
+        <v>15</v>
+      </c>
+      <c r="G169">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170" t="s">
+        <v>422</v>
+      </c>
+      <c r="C170" t="s">
+        <v>111</v>
+      </c>
+      <c r="D170" t="s">
+        <v>512</v>
+      </c>
+      <c r="E170">
+        <v>4</v>
+      </c>
+      <c r="F170">
+        <v>13</v>
+      </c>
+      <c r="G170">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171" t="s">
+        <v>89</v>
+      </c>
+      <c r="C171" t="s">
+        <v>111</v>
+      </c>
+      <c r="D171" t="s">
+        <v>81</v>
+      </c>
+      <c r="E171">
+        <v>6</v>
+      </c>
+      <c r="F171">
+        <v>13</v>
+      </c>
+      <c r="G171">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172" t="s">
+        <v>423</v>
+      </c>
+      <c r="C172" t="s">
+        <v>424</v>
+      </c>
+      <c r="D172" t="s">
+        <v>512</v>
+      </c>
+      <c r="E172">
+        <v>4</v>
+      </c>
+      <c r="F172">
+        <v>10</v>
+      </c>
+      <c r="G172">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173" t="s">
+        <v>425</v>
+      </c>
+      <c r="C173" t="s">
+        <v>304</v>
+      </c>
+      <c r="D173" t="s">
+        <v>295</v>
+      </c>
+      <c r="E173">
+        <v>7</v>
+      </c>
+      <c r="F173">
+        <v>14</v>
+      </c>
+      <c r="G173">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174" t="s">
+        <v>426</v>
+      </c>
+      <c r="C174" t="s">
+        <v>427</v>
+      </c>
+      <c r="D174" t="s">
+        <v>512</v>
+      </c>
+      <c r="E174">
+        <v>7</v>
+      </c>
+      <c r="F174">
+        <v>13</v>
+      </c>
+      <c r="G174">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175" t="s">
+        <v>206</v>
+      </c>
+      <c r="C175" t="s">
+        <v>49</v>
+      </c>
+      <c r="D175" t="s">
+        <v>199</v>
+      </c>
+      <c r="E175">
+        <v>5</v>
+      </c>
+      <c r="F175">
+        <v>11</v>
+      </c>
+      <c r="G175">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176" t="s">
+        <v>208</v>
+      </c>
+      <c r="C176" t="s">
+        <v>209</v>
+      </c>
+      <c r="D176" t="s">
+        <v>207</v>
+      </c>
+      <c r="E176">
+        <v>7</v>
+      </c>
+      <c r="F176">
+        <v>13</v>
+      </c>
+      <c r="G176">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177" t="s">
+        <v>139</v>
+      </c>
+      <c r="C177" t="s">
         <v>156</v>
       </c>
-      <c r="D144" t="s">
-        <v>141</v>
-      </c>
-      <c r="E144">
+      <c r="D177" t="s">
+        <v>138</v>
+      </c>
+      <c r="E177">
         <v>5</v>
       </c>
-      <c r="F144">
+      <c r="F177">
+        <v>12</v>
+      </c>
+      <c r="G177">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178" t="s">
+        <v>428</v>
+      </c>
+      <c r="C178" t="s">
+        <v>429</v>
+      </c>
+      <c r="D178" t="s">
+        <v>512</v>
+      </c>
+      <c r="E178">
+        <v>7</v>
+      </c>
+      <c r="F178">
+        <v>13</v>
+      </c>
+      <c r="G178">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A179">
+        <v>178</v>
+      </c>
+      <c r="B179" t="s">
+        <v>430</v>
+      </c>
+      <c r="C179" t="s">
+        <v>374</v>
+      </c>
+      <c r="D179" t="s">
+        <v>295</v>
+      </c>
+      <c r="E179">
+        <v>1</v>
+      </c>
+      <c r="F179">
+        <v>9</v>
+      </c>
+      <c r="G179">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A180">
+        <v>179</v>
+      </c>
+      <c r="B180" t="s">
+        <v>215</v>
+      </c>
+      <c r="C180" t="s">
+        <v>216</v>
+      </c>
+      <c r="D180" t="s">
+        <v>207</v>
+      </c>
+      <c r="E180">
+        <v>7</v>
+      </c>
+      <c r="F180">
+        <v>13</v>
+      </c>
+      <c r="G180">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A181">
+        <v>180</v>
+      </c>
+      <c r="B181" t="s">
+        <v>431</v>
+      </c>
+      <c r="C181" t="s">
+        <v>306</v>
+      </c>
+      <c r="D181" t="s">
+        <v>512</v>
+      </c>
+      <c r="E181">
+        <v>5</v>
+      </c>
+      <c r="F181">
+        <v>13</v>
+      </c>
+      <c r="G181">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182" t="s">
+        <v>258</v>
+      </c>
+      <c r="C182" t="s">
+        <v>49</v>
+      </c>
+      <c r="D182" t="s">
+        <v>256</v>
+      </c>
+      <c r="E182">
+        <v>5</v>
+      </c>
+      <c r="F182">
+        <v>13</v>
+      </c>
+      <c r="G182">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183" t="s">
+        <v>435</v>
+      </c>
+      <c r="C183" t="s">
+        <v>324</v>
+      </c>
+      <c r="D183" t="s">
+        <v>295</v>
+      </c>
+      <c r="E183">
+        <v>5</v>
+      </c>
+      <c r="F183">
+        <v>13</v>
+      </c>
+      <c r="G183">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184" t="s">
+        <v>436</v>
+      </c>
+      <c r="C184" t="s">
+        <v>437</v>
+      </c>
+      <c r="D184" t="s">
+        <v>512</v>
+      </c>
+      <c r="E184">
+        <v>7</v>
+      </c>
+      <c r="F184">
+        <v>15</v>
+      </c>
+      <c r="G184">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185" t="s">
+        <v>90</v>
+      </c>
+      <c r="C185" t="s">
+        <v>91</v>
+      </c>
+      <c r="D185" t="s">
+        <v>81</v>
+      </c>
+      <c r="E185">
+        <v>4</v>
+      </c>
+      <c r="F185">
+        <v>12</v>
+      </c>
+      <c r="G185">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186" t="s">
+        <v>96</v>
+      </c>
+      <c r="C186" t="s">
+        <v>97</v>
+      </c>
+      <c r="D186" t="s">
+        <v>81</v>
+      </c>
+      <c r="E186">
+        <v>8</v>
+      </c>
+      <c r="F186">
+        <v>14</v>
+      </c>
+      <c r="G186">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187" t="s">
+        <v>92</v>
+      </c>
+      <c r="C187" t="s">
+        <v>93</v>
+      </c>
+      <c r="D187" t="s">
+        <v>81</v>
+      </c>
+      <c r="E187">
+        <v>7</v>
+      </c>
+      <c r="F187">
+        <v>13</v>
+      </c>
+      <c r="G187">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188" t="s">
+        <v>40</v>
+      </c>
+      <c r="C188" t="s">
+        <v>41</v>
+      </c>
+      <c r="D188" t="s">
+        <v>39</v>
+      </c>
+      <c r="E188">
+        <v>4</v>
+      </c>
+      <c r="F188">
+        <v>14</v>
+      </c>
+      <c r="G188">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C189" t="s">
+        <v>101</v>
+      </c>
+      <c r="D189" t="s">
+        <v>512</v>
+      </c>
+      <c r="E189">
+        <v>4</v>
+      </c>
+      <c r="F189">
+        <v>13</v>
+      </c>
+      <c r="G189">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C190" t="s">
+        <v>393</v>
+      </c>
+      <c r="D190" t="s">
+        <v>512</v>
+      </c>
+      <c r="E190">
+        <v>2</v>
+      </c>
+      <c r="F190">
+        <v>10</v>
+      </c>
+      <c r="G190">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C191" t="s">
+        <v>441</v>
+      </c>
+      <c r="D191" t="s">
+        <v>512</v>
+      </c>
+      <c r="E191">
+        <v>7</v>
+      </c>
+      <c r="F191">
+        <v>13</v>
+      </c>
+      <c r="G191">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C192" t="s">
+        <v>443</v>
+      </c>
+      <c r="D192" t="s">
+        <v>295</v>
+      </c>
+      <c r="E192">
+        <v>7</v>
+      </c>
+      <c r="F192">
+        <v>12</v>
+      </c>
+      <c r="G192">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C193" t="s">
+        <v>445</v>
+      </c>
+      <c r="D193" t="s">
+        <v>512</v>
+      </c>
+      <c r="E193">
+        <v>7</v>
+      </c>
+      <c r="F193">
+        <v>13</v>
+      </c>
+      <c r="G193">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C194" t="s">
+        <v>447</v>
+      </c>
+      <c r="D194" t="s">
+        <v>512</v>
+      </c>
+      <c r="E194">
+        <v>7</v>
+      </c>
+      <c r="F194">
+        <v>14</v>
+      </c>
+      <c r="G194">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C195" t="s">
+        <v>449</v>
+      </c>
+      <c r="D195" t="s">
+        <v>512</v>
+      </c>
+      <c r="E195">
+        <v>6</v>
+      </c>
+      <c r="F195">
+        <v>12</v>
+      </c>
+      <c r="G195">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196" t="s">
+        <v>154</v>
+      </c>
+      <c r="C196" t="s">
+        <v>155</v>
+      </c>
+      <c r="D196" t="s">
+        <v>138</v>
+      </c>
+      <c r="E196">
+        <v>8</v>
+      </c>
+      <c r="F196">
+        <v>15</v>
+      </c>
+      <c r="G196">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197" t="s">
+        <v>242</v>
+      </c>
+      <c r="C197" t="s">
+        <v>255</v>
+      </c>
+      <c r="D197" t="s">
+        <v>241</v>
+      </c>
+      <c r="E197">
+        <v>6</v>
+      </c>
+      <c r="F197">
+        <v>12</v>
+      </c>
+      <c r="G197">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A198">
+        <v>197</v>
+      </c>
+      <c r="B198" t="s">
+        <v>452</v>
+      </c>
+      <c r="C198" t="s">
+        <v>453</v>
+      </c>
+      <c r="D198" t="s">
+        <v>512</v>
+      </c>
+      <c r="E198">
+        <v>5</v>
+      </c>
+      <c r="F198">
+        <v>14</v>
+      </c>
+      <c r="G198">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A199">
+        <v>198</v>
+      </c>
+      <c r="B199" t="s">
+        <v>166</v>
+      </c>
+      <c r="C199" t="s">
+        <v>167</v>
+      </c>
+      <c r="D199" t="s">
+        <v>158</v>
+      </c>
+      <c r="E199">
+        <v>6</v>
+      </c>
+      <c r="F199">
+        <v>14</v>
+      </c>
+      <c r="G199">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A200">
+        <v>199</v>
+      </c>
+      <c r="B200" t="s">
+        <v>247</v>
+      </c>
+      <c r="C200" t="s">
+        <v>248</v>
+      </c>
+      <c r="D200" t="s">
+        <v>241</v>
+      </c>
+      <c r="E200">
+        <v>9</v>
+      </c>
+      <c r="F200">
+        <v>15</v>
+      </c>
+      <c r="G200">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201" t="s">
+        <v>454</v>
+      </c>
+      <c r="C201" t="s">
+        <v>248</v>
+      </c>
+      <c r="D201" t="s">
+        <v>512</v>
+      </c>
+      <c r="E201">
+        <v>7</v>
+      </c>
+      <c r="F201">
+        <v>14</v>
+      </c>
+      <c r="G201">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202" t="s">
+        <v>455</v>
+      </c>
+      <c r="C202" t="s">
+        <v>374</v>
+      </c>
+      <c r="D202" t="s">
+        <v>295</v>
+      </c>
+      <c r="E202">
+        <v>6</v>
+      </c>
+      <c r="F202">
+        <v>10</v>
+      </c>
+      <c r="G202">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A203">
+        <v>202</v>
+      </c>
+      <c r="B203" t="s">
+        <v>456</v>
+      </c>
+      <c r="C203" t="s">
+        <v>318</v>
+      </c>
+      <c r="D203" t="s">
+        <v>512</v>
+      </c>
+      <c r="E203">
+        <v>8</v>
+      </c>
+      <c r="F203">
+        <v>13</v>
+      </c>
+      <c r="G203">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A204">
+        <v>203</v>
+      </c>
+      <c r="B204" t="s">
+        <v>69</v>
+      </c>
+      <c r="C204" t="s">
+        <v>30</v>
+      </c>
+      <c r="D204" t="s">
+        <v>67</v>
+      </c>
+      <c r="E204">
+        <v>8</v>
+      </c>
+      <c r="F204">
+        <v>15</v>
+      </c>
+      <c r="G204">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A205">
+        <v>204</v>
+      </c>
+      <c r="B205" t="s">
+        <v>457</v>
+      </c>
+      <c r="C205" t="s">
+        <v>458</v>
+      </c>
+      <c r="D205" t="s">
+        <v>512</v>
+      </c>
+      <c r="E205">
+        <v>4</v>
+      </c>
+      <c r="F205">
+        <v>13</v>
+      </c>
+      <c r="G205">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206" t="s">
+        <v>459</v>
+      </c>
+      <c r="C206" t="s">
+        <v>356</v>
+      </c>
+      <c r="D206" t="s">
+        <v>295</v>
+      </c>
+      <c r="E206">
+        <v>3</v>
+      </c>
+      <c r="F206">
+        <v>13</v>
+      </c>
+      <c r="G206">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207" t="s">
+        <v>210</v>
+      </c>
+      <c r="C207" t="s">
+        <v>211</v>
+      </c>
+      <c r="D207" t="s">
+        <v>207</v>
+      </c>
+      <c r="E207">
+        <v>4</v>
+      </c>
+      <c r="F207">
         <v>11</v>
       </c>
-      <c r="G144">
+      <c r="G207">
         <v>16</v>
       </c>
     </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A208">
+        <v>207</v>
+      </c>
+      <c r="B208" t="s">
+        <v>253</v>
+      </c>
+      <c r="C208" t="s">
+        <v>397</v>
+      </c>
+      <c r="D208" t="s">
+        <v>241</v>
+      </c>
+      <c r="E208">
+        <v>6</v>
+      </c>
+      <c r="F208">
+        <v>13</v>
+      </c>
+      <c r="G208">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A209">
+        <v>208</v>
+      </c>
+      <c r="B209" t="s">
+        <v>123</v>
+      </c>
+      <c r="C209" t="s">
+        <v>124</v>
+      </c>
+      <c r="D209" t="s">
+        <v>116</v>
+      </c>
+      <c r="E209">
+        <v>3</v>
+      </c>
+      <c r="F209">
+        <v>11</v>
+      </c>
+      <c r="G209">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210" t="s">
+        <v>133</v>
+      </c>
+      <c r="C210" t="s">
+        <v>100</v>
+      </c>
+      <c r="D210" t="s">
+        <v>116</v>
+      </c>
+      <c r="E210">
+        <v>8</v>
+      </c>
+      <c r="F210">
+        <v>15</v>
+      </c>
+      <c r="G210">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A211">
+        <v>210</v>
+      </c>
+      <c r="B211" t="s">
+        <v>460</v>
+      </c>
+      <c r="C211" t="s">
+        <v>352</v>
+      </c>
+      <c r="D211" t="s">
+        <v>295</v>
+      </c>
+      <c r="E211">
+        <v>5</v>
+      </c>
+      <c r="F211">
+        <v>12</v>
+      </c>
+      <c r="G211">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A212">
+        <v>211</v>
+      </c>
+      <c r="B212" t="s">
+        <v>249</v>
+      </c>
+      <c r="C212" t="s">
+        <v>250</v>
+      </c>
+      <c r="D212" t="s">
+        <v>241</v>
+      </c>
+      <c r="E212">
+        <v>7</v>
+      </c>
+      <c r="F212">
+        <v>13</v>
+      </c>
+      <c r="G212">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A213">
+        <v>212</v>
+      </c>
+      <c r="B213" t="s">
+        <v>271</v>
+      </c>
+      <c r="C213" t="s">
+        <v>272</v>
+      </c>
+      <c r="D213" t="s">
+        <v>256</v>
+      </c>
+      <c r="E213">
+        <v>4</v>
+      </c>
+      <c r="F213">
+        <v>11</v>
+      </c>
+      <c r="G213">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214" t="s">
+        <v>77</v>
+      </c>
+      <c r="C214" t="s">
+        <v>78</v>
+      </c>
+      <c r="D214" t="s">
+        <v>67</v>
+      </c>
+      <c r="E214">
+        <v>4</v>
+      </c>
+      <c r="F214">
+        <v>12</v>
+      </c>
+      <c r="G214">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A215">
+        <v>214</v>
+      </c>
+      <c r="B215" t="s">
+        <v>461</v>
+      </c>
+      <c r="C215" t="s">
+        <v>462</v>
+      </c>
+      <c r="D215" t="s">
+        <v>295</v>
+      </c>
+      <c r="E215">
+        <v>7</v>
+      </c>
+      <c r="F215">
+        <v>14</v>
+      </c>
+      <c r="G215">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A216">
+        <v>215</v>
+      </c>
+      <c r="B216" t="s">
+        <v>463</v>
+      </c>
+      <c r="C216" t="s">
+        <v>324</v>
+      </c>
+      <c r="D216" t="s">
+        <v>512</v>
+      </c>
+      <c r="E216">
+        <v>6</v>
+      </c>
+      <c r="F216">
+        <v>14</v>
+      </c>
+      <c r="G216">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A217">
+        <v>216</v>
+      </c>
+      <c r="B217" t="s">
+        <v>464</v>
+      </c>
+      <c r="C217" t="s">
+        <v>465</v>
+      </c>
+      <c r="D217" t="s">
+        <v>512</v>
+      </c>
+      <c r="E217">
+        <v>7</v>
+      </c>
+      <c r="F217">
+        <v>13</v>
+      </c>
+      <c r="G217">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A218">
+        <v>217</v>
+      </c>
+      <c r="B218" t="s">
+        <v>466</v>
+      </c>
+      <c r="C218" t="s">
+        <v>301</v>
+      </c>
+      <c r="D218" t="s">
+        <v>295</v>
+      </c>
+      <c r="E218">
+        <v>3</v>
+      </c>
+      <c r="F218">
+        <v>12</v>
+      </c>
+      <c r="G218">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A219">
+        <v>218</v>
+      </c>
+      <c r="B219" t="s">
+        <v>121</v>
+      </c>
+      <c r="C219" t="s">
+        <v>122</v>
+      </c>
+      <c r="D219" t="s">
+        <v>116</v>
+      </c>
+      <c r="E219">
+        <v>6</v>
+      </c>
+      <c r="F219">
+        <v>13</v>
+      </c>
+      <c r="G219">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A220">
+        <v>219</v>
+      </c>
+      <c r="B220" t="s">
+        <v>467</v>
+      </c>
+      <c r="C220" t="s">
+        <v>468</v>
+      </c>
+      <c r="D220" t="s">
+        <v>512</v>
+      </c>
+      <c r="E220">
+        <v>2</v>
+      </c>
+      <c r="F220">
+        <v>13</v>
+      </c>
+      <c r="G220">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A221">
+        <v>220</v>
+      </c>
+      <c r="B221" t="s">
+        <v>469</v>
+      </c>
+      <c r="C221" t="s">
+        <v>470</v>
+      </c>
+      <c r="D221" t="s">
+        <v>512</v>
+      </c>
+      <c r="E221">
+        <v>7</v>
+      </c>
+      <c r="F221">
+        <v>13</v>
+      </c>
+      <c r="G221">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A222">
+        <v>221</v>
+      </c>
+      <c r="B222" t="s">
+        <v>53</v>
+      </c>
+      <c r="C222" t="s">
+        <v>54</v>
+      </c>
+      <c r="D222" t="s">
+        <v>50</v>
+      </c>
+      <c r="E222">
+        <v>5</v>
+      </c>
+      <c r="F222">
+        <v>13</v>
+      </c>
+      <c r="G222">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223" t="s">
+        <v>65</v>
+      </c>
+      <c r="C223" t="s">
+        <v>66</v>
+      </c>
+      <c r="D223" t="s">
+        <v>50</v>
+      </c>
+      <c r="E223">
+        <v>7</v>
+      </c>
+      <c r="F223">
+        <v>14</v>
+      </c>
+      <c r="G223">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224" t="s">
+        <v>471</v>
+      </c>
+      <c r="C224" t="s">
+        <v>472</v>
+      </c>
+      <c r="D224" t="s">
+        <v>512</v>
+      </c>
+      <c r="E224">
+        <v>7</v>
+      </c>
+      <c r="F224">
+        <v>12</v>
+      </c>
+      <c r="G224">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225" t="s">
+        <v>473</v>
+      </c>
+      <c r="C225" t="s">
+        <v>474</v>
+      </c>
+      <c r="D225" t="s">
+        <v>512</v>
+      </c>
+      <c r="E225">
+        <v>4</v>
+      </c>
+      <c r="F225">
+        <v>13</v>
+      </c>
+      <c r="G225">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226" t="s">
+        <v>475</v>
+      </c>
+      <c r="C226" t="s">
+        <v>393</v>
+      </c>
+      <c r="D226" t="s">
+        <v>512</v>
+      </c>
+      <c r="E226">
+        <v>7</v>
+      </c>
+      <c r="F226">
+        <v>13</v>
+      </c>
+      <c r="G226">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227" t="s">
+        <v>476</v>
+      </c>
+      <c r="C227" t="s">
+        <v>374</v>
+      </c>
+      <c r="D227" t="s">
+        <v>295</v>
+      </c>
+      <c r="E227">
+        <v>1</v>
+      </c>
+      <c r="F227">
+        <v>11</v>
+      </c>
+      <c r="G227">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228" t="s">
+        <v>142</v>
+      </c>
+      <c r="C228" t="s">
+        <v>54</v>
+      </c>
+      <c r="D228" t="s">
+        <v>138</v>
+      </c>
+      <c r="E228">
+        <v>6</v>
+      </c>
+      <c r="F228">
+        <v>13</v>
+      </c>
+      <c r="G228">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229" t="s">
+        <v>477</v>
+      </c>
+      <c r="C229" t="s">
+        <v>478</v>
+      </c>
+      <c r="D229" t="s">
+        <v>512</v>
+      </c>
+      <c r="E229">
+        <v>7</v>
+      </c>
+      <c r="F229">
+        <v>15</v>
+      </c>
+      <c r="G229">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230" t="s">
+        <v>479</v>
+      </c>
+      <c r="C230" t="s">
+        <v>480</v>
+      </c>
+      <c r="D230" t="s">
+        <v>512</v>
+      </c>
+      <c r="E230">
+        <v>8</v>
+      </c>
+      <c r="F230">
+        <v>12</v>
+      </c>
+      <c r="G230">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231" t="s">
+        <v>481</v>
+      </c>
+      <c r="C231">
+        <v>-45</v>
+      </c>
+      <c r="D231" t="s">
+        <v>512</v>
+      </c>
+      <c r="E231">
+        <v>7</v>
+      </c>
+      <c r="F231">
+        <v>13</v>
+      </c>
+      <c r="G231">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A232">
+        <v>231</v>
+      </c>
+      <c r="B232" t="s">
+        <v>145</v>
+      </c>
+      <c r="C232" t="s">
+        <v>146</v>
+      </c>
+      <c r="D232" t="s">
+        <v>138</v>
+      </c>
+      <c r="E232">
+        <v>5</v>
+      </c>
+      <c r="F232">
+        <v>11</v>
+      </c>
+      <c r="G232">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A233">
+        <v>232</v>
+      </c>
+      <c r="B233" t="s">
+        <v>482</v>
+      </c>
+      <c r="C233" t="s">
+        <v>483</v>
+      </c>
+      <c r="D233" t="s">
+        <v>512</v>
+      </c>
+      <c r="E233">
+        <v>6</v>
+      </c>
+      <c r="F233">
+        <v>15</v>
+      </c>
+      <c r="G233">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A234">
+        <v>233</v>
+      </c>
+      <c r="B234" t="s">
+        <v>94</v>
+      </c>
+      <c r="C234" t="s">
+        <v>112</v>
+      </c>
+      <c r="D234" t="s">
+        <v>81</v>
+      </c>
+      <c r="E234">
+        <v>7</v>
+      </c>
+      <c r="F234">
+        <v>14</v>
+      </c>
+      <c r="G234">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A235">
+        <v>234</v>
+      </c>
+      <c r="B235" t="s">
+        <v>484</v>
+      </c>
+      <c r="C235" t="s">
+        <v>485</v>
+      </c>
+      <c r="D235" t="s">
+        <v>512</v>
+      </c>
+      <c r="E235">
+        <v>5</v>
+      </c>
+      <c r="F235">
+        <v>11</v>
+      </c>
+      <c r="G235">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A236">
+        <v>235</v>
+      </c>
+      <c r="B236" t="s">
+        <v>95</v>
+      </c>
+      <c r="C236" t="s">
+        <v>113</v>
+      </c>
+      <c r="D236" t="s">
+        <v>81</v>
+      </c>
+      <c r="E236">
+        <v>3</v>
+      </c>
+      <c r="F236">
+        <v>10</v>
+      </c>
+      <c r="G236">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A237">
+        <v>236</v>
+      </c>
+      <c r="B237" t="s">
+        <v>134</v>
+      </c>
+      <c r="C237" t="s">
+        <v>135</v>
+      </c>
+      <c r="D237" t="s">
+        <v>116</v>
+      </c>
+      <c r="E237">
+        <v>4</v>
+      </c>
+      <c r="F237">
+        <v>12</v>
+      </c>
+      <c r="G237">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A238">
+        <v>237</v>
+      </c>
+      <c r="B238" t="s">
+        <v>486</v>
+      </c>
+      <c r="C238" t="s">
+        <v>487</v>
+      </c>
+      <c r="D238" t="s">
+        <v>512</v>
+      </c>
+      <c r="E238">
+        <v>5</v>
+      </c>
+      <c r="F238">
+        <v>13</v>
+      </c>
+      <c r="G238">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A239">
+        <v>238</v>
+      </c>
+      <c r="B239" t="s">
+        <v>488</v>
+      </c>
+      <c r="C239" t="s">
+        <v>489</v>
+      </c>
+      <c r="D239" t="s">
+        <v>512</v>
+      </c>
+      <c r="E239">
+        <v>6</v>
+      </c>
+      <c r="F239">
+        <v>14</v>
+      </c>
+      <c r="G239">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A240">
+        <v>239</v>
+      </c>
+      <c r="B240" t="s">
+        <v>490</v>
+      </c>
+      <c r="C240" t="s">
+        <v>491</v>
+      </c>
+      <c r="D240" t="s">
+        <v>512</v>
+      </c>
+      <c r="E240">
+        <v>3</v>
+      </c>
+      <c r="F240">
+        <v>10</v>
+      </c>
+      <c r="G240">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A241">
+        <v>240</v>
+      </c>
+      <c r="B241" t="s">
+        <v>202</v>
+      </c>
+      <c r="C241" t="s">
+        <v>201</v>
+      </c>
+      <c r="D241" t="s">
+        <v>199</v>
+      </c>
+      <c r="E241">
+        <v>4</v>
+      </c>
+      <c r="F241">
+        <v>7</v>
+      </c>
+      <c r="G241">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A242">
+        <v>241</v>
+      </c>
+      <c r="B242" t="s">
+        <v>492</v>
+      </c>
+      <c r="C242" t="s">
+        <v>485</v>
+      </c>
+      <c r="D242" t="s">
+        <v>512</v>
+      </c>
+      <c r="E242">
+        <v>7</v>
+      </c>
+      <c r="F242">
+        <v>10</v>
+      </c>
+      <c r="G242">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A243">
+        <v>242</v>
+      </c>
+      <c r="B243" t="s">
+        <v>493</v>
+      </c>
+      <c r="C243" t="s">
+        <v>374</v>
+      </c>
+      <c r="D243" t="s">
+        <v>512</v>
+      </c>
+      <c r="E243">
+        <v>4</v>
+      </c>
+      <c r="F243">
+        <v>14</v>
+      </c>
+      <c r="G243">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A244">
+        <v>243</v>
+      </c>
+      <c r="B244" t="s">
+        <v>237</v>
+      </c>
+      <c r="C244" t="s">
+        <v>286</v>
+      </c>
+      <c r="D244" t="s">
+        <v>224</v>
+      </c>
+      <c r="E244">
+        <v>3</v>
+      </c>
+      <c r="F244">
+        <v>10</v>
+      </c>
+      <c r="G244">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A245">
+        <v>244</v>
+      </c>
+      <c r="B245" t="s">
+        <v>494</v>
+      </c>
+      <c r="C245" t="s">
+        <v>495</v>
+      </c>
+      <c r="D245" t="s">
+        <v>512</v>
+      </c>
+      <c r="E245">
+        <v>6</v>
+      </c>
+      <c r="F245">
+        <v>12</v>
+      </c>
+      <c r="G245">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A246">
+        <v>245</v>
+      </c>
+      <c r="B246" t="s">
+        <v>496</v>
+      </c>
+      <c r="C246" t="s">
+        <v>414</v>
+      </c>
+      <c r="D246" t="s">
+        <v>512</v>
+      </c>
+      <c r="E246">
+        <v>3</v>
+      </c>
+      <c r="F246">
+        <v>12</v>
+      </c>
+      <c r="G246">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A247">
+        <v>246</v>
+      </c>
+      <c r="B247" t="s">
+        <v>497</v>
+      </c>
+      <c r="C247" t="s">
+        <v>465</v>
+      </c>
+      <c r="D247" t="s">
+        <v>512</v>
+      </c>
+      <c r="E247">
+        <v>6</v>
+      </c>
+      <c r="F247">
+        <v>13</v>
+      </c>
+      <c r="G247">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A248">
+        <v>247</v>
+      </c>
+      <c r="B248" t="s">
+        <v>231</v>
+      </c>
+      <c r="C248" t="s">
+        <v>122</v>
+      </c>
+      <c r="D248" t="s">
+        <v>224</v>
+      </c>
+      <c r="E248">
+        <v>8</v>
+      </c>
+      <c r="F248">
+        <v>15</v>
+      </c>
+      <c r="G248">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A249">
+        <v>248</v>
+      </c>
+      <c r="B249" t="s">
+        <v>223</v>
+      </c>
+      <c r="C249" t="s">
+        <v>220</v>
+      </c>
+      <c r="D249" t="s">
+        <v>207</v>
+      </c>
+      <c r="E249">
+        <v>7</v>
+      </c>
+      <c r="F249">
+        <v>14</v>
+      </c>
+      <c r="G249">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A250">
+        <v>249</v>
+      </c>
+      <c r="B250" t="s">
+        <v>22</v>
+      </c>
+      <c r="C250" t="s">
+        <v>23</v>
+      </c>
+      <c r="D250" t="s">
+        <v>27</v>
+      </c>
+      <c r="E250">
+        <v>8</v>
+      </c>
+      <c r="F250">
+        <v>15</v>
+      </c>
+      <c r="G250">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A251">
+        <v>250</v>
+      </c>
+      <c r="B251" t="s">
+        <v>229</v>
+      </c>
+      <c r="C251" t="s">
+        <v>230</v>
+      </c>
+      <c r="D251" t="s">
+        <v>224</v>
+      </c>
+      <c r="E251">
+        <v>8</v>
+      </c>
+      <c r="F251">
+        <v>14</v>
+      </c>
+      <c r="G251">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A252">
+        <v>251</v>
+      </c>
+      <c r="B252" t="s">
+        <v>164</v>
+      </c>
+      <c r="C252" t="s">
+        <v>165</v>
+      </c>
+      <c r="D252" t="s">
+        <v>158</v>
+      </c>
+      <c r="E252">
+        <v>8</v>
+      </c>
+      <c r="F252">
+        <v>14</v>
+      </c>
+      <c r="G252">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A253">
+        <v>252</v>
+      </c>
+      <c r="B253" t="s">
+        <v>125</v>
+      </c>
+      <c r="C253" t="s">
+        <v>126</v>
+      </c>
+      <c r="D253" t="s">
+        <v>116</v>
+      </c>
+      <c r="E253">
+        <v>7</v>
+      </c>
+      <c r="F253">
+        <v>14</v>
+      </c>
+      <c r="G253">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A254">
+        <v>253</v>
+      </c>
+      <c r="B254" t="s">
+        <v>225</v>
+      </c>
+      <c r="C254" t="s">
+        <v>226</v>
+      </c>
+      <c r="D254" t="s">
+        <v>224</v>
+      </c>
+      <c r="E254">
+        <v>5</v>
+      </c>
+      <c r="F254">
+        <v>11</v>
+      </c>
+      <c r="G254">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A255">
+        <v>254</v>
+      </c>
+      <c r="B255" t="s">
+        <v>31</v>
+      </c>
+      <c r="C255" t="s">
+        <v>32</v>
+      </c>
+      <c r="D255" t="s">
+        <v>28</v>
+      </c>
+      <c r="E255">
+        <v>8</v>
+      </c>
+      <c r="F255">
+        <v>15</v>
+      </c>
+      <c r="G255">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A256">
+        <v>255</v>
+      </c>
+      <c r="B256" t="s">
+        <v>498</v>
+      </c>
+      <c r="C256" t="s">
+        <v>368</v>
+      </c>
+      <c r="D256" t="s">
+        <v>512</v>
+      </c>
+      <c r="E256">
+        <v>4</v>
+      </c>
+      <c r="F256">
+        <v>14</v>
+      </c>
+      <c r="G256">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A257">
+        <v>256</v>
+      </c>
+      <c r="B257" t="s">
+        <v>48</v>
+      </c>
+      <c r="C257" t="s">
+        <v>49</v>
+      </c>
+      <c r="D257" t="s">
+        <v>39</v>
+      </c>
+      <c r="E257">
+        <v>5</v>
+      </c>
+      <c r="F257">
+        <v>14</v>
+      </c>
+      <c r="G257">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A258">
+        <v>257</v>
+      </c>
+      <c r="B258" t="s">
+        <v>33</v>
+      </c>
+      <c r="C258" t="s">
+        <v>34</v>
+      </c>
+      <c r="D258" t="s">
+        <v>28</v>
+      </c>
+      <c r="E258">
+        <v>5</v>
+      </c>
+      <c r="F258">
+        <v>12</v>
+      </c>
+      <c r="G258">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A259">
+        <v>258</v>
+      </c>
+      <c r="B259" t="s">
+        <v>214</v>
+      </c>
+      <c r="C259" t="s">
+        <v>108</v>
+      </c>
+      <c r="D259" t="s">
+        <v>207</v>
+      </c>
+      <c r="E259">
+        <v>8</v>
+      </c>
+      <c r="F259">
+        <v>12</v>
+      </c>
+      <c r="G259">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A260">
+        <v>259</v>
+      </c>
+      <c r="B260" t="s">
+        <v>35</v>
+      </c>
+      <c r="C260" t="s">
+        <v>36</v>
+      </c>
+      <c r="D260" t="s">
+        <v>28</v>
+      </c>
+      <c r="E260">
+        <v>7</v>
+      </c>
+      <c r="F260">
+        <v>12</v>
+      </c>
+      <c r="G260">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A261">
+        <v>260</v>
+      </c>
+      <c r="B261" t="s">
+        <v>450</v>
+      </c>
+      <c r="C261" t="s">
+        <v>451</v>
+      </c>
+      <c r="D261" t="s">
+        <v>512</v>
+      </c>
+      <c r="E261">
+        <v>5</v>
+      </c>
+      <c r="F261">
+        <v>13</v>
+      </c>
+      <c r="G261">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A262">
+        <v>261</v>
+      </c>
+      <c r="B262" t="s">
+        <v>178</v>
+      </c>
+      <c r="C262" t="s">
+        <v>179</v>
+      </c>
+      <c r="D262" t="s">
+        <v>175</v>
+      </c>
+      <c r="E262">
+        <v>5</v>
+      </c>
+      <c r="F262">
+        <v>13</v>
+      </c>
+      <c r="G262">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A263">
+        <v>262</v>
+      </c>
+      <c r="B263" t="s">
+        <v>502</v>
+      </c>
+      <c r="C263" t="s">
+        <v>503</v>
+      </c>
+      <c r="D263" t="s">
+        <v>512</v>
+      </c>
+      <c r="E263">
+        <v>9</v>
+      </c>
+      <c r="F263">
+        <v>14</v>
+      </c>
+      <c r="G263">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A264">
+        <v>263</v>
+      </c>
+      <c r="B264" t="s">
+        <v>504</v>
+      </c>
+      <c r="C264" t="s">
+        <v>370</v>
+      </c>
+      <c r="D264" t="s">
+        <v>295</v>
+      </c>
+      <c r="E264">
+        <v>3</v>
+      </c>
+      <c r="F264">
+        <v>11</v>
+      </c>
+      <c r="G264">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A265">
+        <v>264</v>
+      </c>
+      <c r="B265" t="s">
+        <v>240</v>
+      </c>
+      <c r="C265" t="s">
+        <v>235</v>
+      </c>
+      <c r="D265" t="s">
+        <v>224</v>
+      </c>
+      <c r="E265">
+        <v>8</v>
+      </c>
+      <c r="F265">
+        <v>14</v>
+      </c>
+      <c r="G265">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A266">
+        <v>265</v>
+      </c>
+      <c r="B266" t="s">
+        <v>11</v>
+      </c>
+      <c r="C266" t="s">
+        <v>12</v>
+      </c>
+      <c r="D266" t="s">
+        <v>17</v>
+      </c>
+      <c r="E266">
+        <v>8</v>
+      </c>
+      <c r="F266">
+        <v>15</v>
+      </c>
+      <c r="G266">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A267">
+        <v>266</v>
+      </c>
+      <c r="B267" t="s">
+        <v>257</v>
+      </c>
+      <c r="C267" t="s">
+        <v>213</v>
+      </c>
+      <c r="D267" t="s">
+        <v>256</v>
+      </c>
+      <c r="E267">
+        <v>9</v>
+      </c>
+      <c r="F267">
+        <v>15</v>
+      </c>
+      <c r="G267">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A268">
+        <v>267</v>
+      </c>
+      <c r="B268" t="s">
+        <v>507</v>
+      </c>
+      <c r="C268" t="s">
+        <v>508</v>
+      </c>
+      <c r="D268" t="s">
+        <v>512</v>
+      </c>
+      <c r="E268">
+        <v>7</v>
+      </c>
+      <c r="F268">
+        <v>13</v>
+      </c>
+      <c r="G268">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A269">
+        <v>268</v>
+      </c>
+      <c r="B269" t="s">
+        <v>499</v>
+      </c>
+      <c r="C269" t="s">
+        <v>500</v>
+      </c>
+      <c r="D269" t="s">
+        <v>512</v>
+      </c>
+      <c r="E269">
+        <v>2</v>
+      </c>
+      <c r="F269">
+        <v>10</v>
+      </c>
+      <c r="G269">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A270">
+        <v>269</v>
+      </c>
+      <c r="B270" t="s">
+        <v>195</v>
+      </c>
+      <c r="C270" t="s">
+        <v>186</v>
+      </c>
+      <c r="D270" t="s">
+        <v>185</v>
+      </c>
+      <c r="E270">
+        <v>7</v>
+      </c>
+      <c r="F270">
+        <v>13</v>
+      </c>
+      <c r="G270">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A271">
+        <v>270</v>
+      </c>
+      <c r="B271" t="s">
+        <v>509</v>
+      </c>
+      <c r="C271" t="s">
+        <v>510</v>
+      </c>
+      <c r="D271" t="s">
+        <v>512</v>
+      </c>
+      <c r="E271">
+        <v>6</v>
+      </c>
+      <c r="F271">
+        <v>12</v>
+      </c>
+      <c r="G271">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A272">
+        <v>271</v>
+      </c>
+      <c r="B272" t="s">
+        <v>505</v>
+      </c>
+      <c r="C272" t="s">
+        <v>506</v>
+      </c>
+      <c r="D272" t="s">
+        <v>512</v>
+      </c>
+      <c r="E272">
+        <v>7</v>
+      </c>
+      <c r="F272">
+        <v>13</v>
+      </c>
+      <c r="G272">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A273">
+        <v>272</v>
+      </c>
+      <c r="B273" t="s">
+        <v>511</v>
+      </c>
+      <c r="C273" t="s">
+        <v>213</v>
+      </c>
+      <c r="D273" t="s">
+        <v>512</v>
+      </c>
+      <c r="E273">
+        <v>6</v>
+      </c>
+      <c r="F273">
+        <v>14</v>
+      </c>
+      <c r="G273">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A274">
+        <v>273</v>
+      </c>
+      <c r="B274" t="s">
+        <v>187</v>
+      </c>
+      <c r="C274" t="s">
+        <v>186</v>
+      </c>
+      <c r="D274" t="s">
+        <v>185</v>
+      </c>
+      <c r="E274">
+        <v>4</v>
+      </c>
+      <c r="F274">
+        <v>11</v>
+      </c>
+      <c r="G274">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A275">
+        <v>274</v>
+      </c>
+      <c r="B275" t="s">
+        <v>501</v>
+      </c>
+      <c r="C275" t="s">
+        <v>339</v>
+      </c>
+      <c r="D275" t="s">
+        <v>512</v>
+      </c>
+      <c r="E275">
+        <v>5</v>
+      </c>
+      <c r="F275">
+        <v>10</v>
+      </c>
+      <c r="G275">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A276">
+        <v>275</v>
+      </c>
+      <c r="B276" t="s">
+        <v>107</v>
+      </c>
+      <c r="C276" t="s">
+        <v>109</v>
+      </c>
+      <c r="D276" t="s">
+        <v>81</v>
+      </c>
+      <c r="E276">
+        <v>6</v>
+      </c>
+      <c r="F276">
+        <v>12</v>
+      </c>
+      <c r="G276">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A277">
+        <v>276</v>
+      </c>
+      <c r="B277" t="s">
+        <v>259</v>
+      </c>
+      <c r="C277" t="s">
+        <v>260</v>
+      </c>
+      <c r="D277" t="s">
+        <v>256</v>
+      </c>
+      <c r="E277">
+        <v>6</v>
+      </c>
+      <c r="F277">
+        <v>13</v>
+      </c>
+      <c r="G277">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A278">
+        <v>277</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C278" t="s">
+        <v>434</v>
+      </c>
+      <c r="D278" t="s">
+        <v>512</v>
+      </c>
+      <c r="E278">
+        <v>2</v>
+      </c>
+      <c r="F278">
+        <v>11</v>
+      </c>
+      <c r="G278">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A279">
+        <v>278</v>
+      </c>
+      <c r="B279" t="s">
+        <v>137</v>
+      </c>
+      <c r="C279" t="s">
+        <v>129</v>
+      </c>
+      <c r="D279" t="s">
+        <v>116</v>
+      </c>
+      <c r="E279">
+        <v>7</v>
+      </c>
+      <c r="F279">
+        <v>14</v>
+      </c>
+      <c r="G279">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A280">
+        <v>279</v>
+      </c>
+      <c r="B280" t="s">
+        <v>80</v>
+      </c>
+      <c r="C280" t="s">
+        <v>79</v>
+      </c>
+      <c r="D280" t="s">
+        <v>67</v>
+      </c>
+      <c r="E280">
+        <v>5</v>
+      </c>
+      <c r="F280">
+        <v>10</v>
+      </c>
+      <c r="G280">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A281">
+        <v>280</v>
+      </c>
+      <c r="B281" t="s">
+        <v>136</v>
+      </c>
+      <c r="C281" t="s">
+        <v>130</v>
+      </c>
+      <c r="D281" t="s">
+        <v>116</v>
+      </c>
+      <c r="E281">
+        <v>6</v>
+      </c>
+      <c r="F281">
+        <v>13</v>
+      </c>
+      <c r="G281">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A282">
+        <v>281</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C282" t="s">
+        <v>153</v>
+      </c>
+      <c r="D282" t="s">
+        <v>138</v>
+      </c>
+      <c r="E282">
+        <v>5</v>
+      </c>
+      <c r="F282">
+        <v>11</v>
+      </c>
+      <c r="G282">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A283">
+        <v>282</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C283" t="s">
+        <v>374</v>
+      </c>
+      <c r="D283" t="s">
+        <v>295</v>
+      </c>
+      <c r="E283">
+        <v>4</v>
+      </c>
+      <c r="F283">
+        <v>12</v>
+      </c>
+      <c r="G283">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H144" xr:uid="{F48EBC91-EB0A-4513-A427-E3024C547FB9}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H144">
-      <sortCondition ref="B1:B144"/>
+  <autoFilter ref="A1:H283" xr:uid="{F48EBC91-EB0A-4513-A427-E3024C547FB9}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H283">
+      <sortCondition ref="B1:B283"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
